--- a/grupos/1AV - Estadisticos 20241.xlsx
+++ b/grupos/1AV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="112">
   <si>
     <t>Materia</t>
   </si>
@@ -218,24 +218,24 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Valerio González Valeria</t>
+  </si>
+  <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
+    <t>Silva Villegas Mario</t>
+  </si>
+  <si>
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
-    <t>Valerio González Valeria</t>
-  </si>
-  <si>
-    <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
-    <t>Silva Villegas Mario</t>
-  </si>
-  <si>
     <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
@@ -254,157 +254,106 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>EDILBERTO</t>
-  </si>
-  <si>
-    <t>ARMAS</t>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>RIOS</t>
   </si>
   <si>
     <t>CAMACHO</t>
   </si>
   <si>
-    <t>ESCOBAR</t>
+    <t>CHONCOA</t>
   </si>
   <si>
     <t>FERNANDEZ</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>MENDEZ</t>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>MORALES</t>
   </si>
   <si>
     <t>MUÑOZ</t>
   </si>
   <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>CHONCOA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
+    <t>ROJAS</t>
   </si>
   <si>
     <t>VILLEGAS</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>SALINAS</t>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
     <t>MARQUEZ</t>
   </si>
   <si>
+    <t>CORTES</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>PAYRO</t>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>CUAHUA</t>
   </si>
   <si>
     <t>CORONA</t>
   </si>
   <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>VALLEJOS</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>JOSE GUSTAVO</t>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>URIEL ARTURO</t>
+  </si>
+  <si>
+    <t>UZIEL</t>
   </si>
   <si>
     <t>ALEXANDRO</t>
   </si>
   <si>
-    <t>CARMEN STEFANY</t>
+    <t>EMMANUEL GUADALUPE</t>
   </si>
   <si>
     <t>CRISTAL</t>
   </si>
   <si>
+    <t>ADOLFO</t>
+  </si>
+  <si>
     <t>BRYANA</t>
   </si>
   <si>
-    <t>RAMSES</t>
+    <t>BRAYAN</t>
+  </si>
+  <si>
+    <t>ANDRES</t>
   </si>
   <si>
     <t>JOSE ABEL</t>
   </si>
   <si>
-    <t>UZIEL</t>
-  </si>
-  <si>
-    <t>SERGIO GISELL</t>
-  </si>
-  <si>
-    <t>EMMANUEL GUADALUPE</t>
-  </si>
-  <si>
-    <t>NAHUM OMAR</t>
-  </si>
-  <si>
-    <t>ADOLFO</t>
-  </si>
-  <si>
-    <t>YOSGART</t>
-  </si>
-  <si>
-    <t>BRAYAN</t>
-  </si>
-  <si>
-    <t>KEVIN ZAID</t>
+    <t>LUIS ROBERTO</t>
   </si>
   <si>
     <t>MAURICIO</t>
-  </si>
-  <si>
-    <t>JOSMAR</t>
   </si>
 </sst>
 </file>
@@ -950,25 +899,25 @@
         <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q4">
         <v>-1</v>
@@ -1007,16 +956,16 @@
         <v>5</v>
       </c>
       <c r="AC4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AD4">
         <v>5</v>
       </c>
       <c r="AE4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG4">
         <v>10</v>
@@ -1051,25 +1000,25 @@
         <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q5">
         <v>-1</v>
@@ -1105,19 +1054,19 @@
         <v>8</v>
       </c>
       <c r="AB5">
+        <v>8</v>
+      </c>
+      <c r="AC5">
+        <v>8</v>
+      </c>
+      <c r="AD5">
+        <v>7</v>
+      </c>
+      <c r="AE5">
         <v>9</v>
       </c>
-      <c r="AC5">
-        <v>6</v>
-      </c>
-      <c r="AD5">
-        <v>6</v>
-      </c>
-      <c r="AE5">
-        <v>10</v>
-      </c>
       <c r="AF5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG5">
         <v>10</v>
@@ -1152,25 +1101,25 @@
         <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q6">
         <v>-1</v>
@@ -1203,7 +1152,7 @@
         <v>6</v>
       </c>
       <c r="AA6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB6">
         <v>5</v>
@@ -1253,25 +1202,25 @@
         <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q7">
         <v>-1</v>
@@ -1310,7 +1259,7 @@
         <v>5</v>
       </c>
       <c r="AC7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD7">
         <v>5</v>
@@ -1319,7 +1268,7 @@
         <v>6</v>
       </c>
       <c r="AF7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG7">
         <v>10</v>
@@ -1354,25 +1303,25 @@
         <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q8">
         <v>-1</v>
@@ -1402,25 +1351,25 @@
         <v>-1</v>
       </c>
       <c r="Z8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB8">
         <v>6</v>
       </c>
       <c r="AC8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE8">
         <v>7</v>
       </c>
       <c r="AF8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG8">
         <v>10</v>
@@ -1455,25 +1404,25 @@
         <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q9">
         <v>-1</v>
@@ -1503,7 +1452,7 @@
         <v>-1</v>
       </c>
       <c r="Z9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA9">
         <v>9</v>
@@ -1512,13 +1461,13 @@
         <v>5</v>
       </c>
       <c r="AC9">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AD9">
         <v>6</v>
       </c>
       <c r="AE9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF9">
         <v>7</v>
@@ -1556,25 +1505,25 @@
         <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q10">
         <v>-1</v>
@@ -1604,7 +1553,7 @@
         <v>-1</v>
       </c>
       <c r="Z10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA10">
         <v>8</v>
@@ -1616,10 +1565,10 @@
         <v>5</v>
       </c>
       <c r="AD10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF10">
         <v>5</v>
@@ -1657,25 +1606,25 @@
         <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q11">
         <v>-1</v>
@@ -1720,7 +1669,7 @@
         <v>5</v>
       </c>
       <c r="AE11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF11">
         <v>6</v>
@@ -1758,25 +1707,25 @@
         <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q12">
         <v>-1</v>
@@ -1806,10 +1755,10 @@
         <v>-1</v>
       </c>
       <c r="Z12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB12">
         <v>5</v>
@@ -1859,25 +1808,25 @@
         <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
         <v>-1</v>
@@ -1907,25 +1856,25 @@
         <v>-1</v>
       </c>
       <c r="Z13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA13">
         <v>6</v>
       </c>
       <c r="AB13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AD13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE13">
         <v>7</v>
       </c>
       <c r="AF13">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG13">
         <v>10</v>
@@ -1960,25 +1909,25 @@
         <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q14">
         <v>-1</v>
@@ -2014,19 +1963,19 @@
         <v>6</v>
       </c>
       <c r="AB14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AD14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG14">
         <v>10</v>
@@ -2061,25 +2010,25 @@
         <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
         <v>-1</v>
@@ -2112,22 +2061,22 @@
         <v>9</v>
       </c>
       <c r="AA15">
+        <v>8</v>
+      </c>
+      <c r="AB15">
+        <v>8</v>
+      </c>
+      <c r="AC15">
         <v>9</v>
       </c>
-      <c r="AB15">
-        <v>7</v>
-      </c>
-      <c r="AC15">
-        <v>7</v>
-      </c>
       <c r="AD15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE15">
         <v>10</v>
       </c>
       <c r="AF15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AG15">
         <v>10</v>
@@ -2162,25 +2111,25 @@
         <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
         <v>-1</v>
@@ -2210,25 +2159,25 @@
         <v>-1</v>
       </c>
       <c r="Z16">
+        <v>8</v>
+      </c>
+      <c r="AA16">
         <v>9</v>
       </c>
-      <c r="AA16">
-        <v>10</v>
-      </c>
       <c r="AB16">
         <v>8</v>
       </c>
       <c r="AC16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE16">
         <v>10</v>
       </c>
       <c r="AF16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG16">
         <v>10</v>
@@ -2263,25 +2212,25 @@
         <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q17">
         <v>-1</v>
@@ -2314,7 +2263,7 @@
         <v>5</v>
       </c>
       <c r="AA17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB17">
         <v>5</v>
@@ -2323,10 +2272,10 @@
         <v>5</v>
       </c>
       <c r="AD17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF17">
         <v>6</v>
@@ -2364,25 +2313,25 @@
         <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q18">
         <v>-1</v>
@@ -2424,10 +2373,10 @@
         <v>5</v>
       </c>
       <c r="AD18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF18">
         <v>5</v>
@@ -2465,25 +2414,25 @@
         <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q19">
         <v>-1</v>
@@ -2513,7 +2462,7 @@
         <v>-1</v>
       </c>
       <c r="Z19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA19">
         <v>7</v>
@@ -2528,7 +2477,7 @@
         <v>5</v>
       </c>
       <c r="AE19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF19">
         <v>6</v>
@@ -2566,25 +2515,25 @@
         <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q20">
         <v>-1</v>
@@ -2617,22 +2566,22 @@
         <v>7</v>
       </c>
       <c r="AA20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE20">
         <v>8</v>
       </c>
       <c r="AF20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG20">
         <v>10</v>
@@ -2667,25 +2616,25 @@
         <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q21">
         <v>-1</v>
@@ -2718,19 +2667,19 @@
         <v>7</v>
       </c>
       <c r="AA21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC21">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AD21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF21">
         <v>7</v>
@@ -2768,25 +2717,25 @@
         <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q22">
         <v>-1</v>
@@ -2834,7 +2783,7 @@
         <v>9</v>
       </c>
       <c r="AF22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG22">
         <v>10</v>
@@ -2869,25 +2818,25 @@
         <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q23">
         <v>-1</v>
@@ -2923,19 +2872,19 @@
         <v>5</v>
       </c>
       <c r="AB23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC23">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AD23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF23">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AG23">
         <v>10</v>
@@ -2970,25 +2919,25 @@
         <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q24">
         <v>-1</v>
@@ -3018,25 +2967,25 @@
         <v>-1</v>
       </c>
       <c r="Z24">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE24">
         <v>6</v>
       </c>
       <c r="AF24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG24">
         <v>10</v>
@@ -3071,25 +3020,25 @@
         <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q25">
         <v>-1</v>
@@ -3119,25 +3068,25 @@
         <v>-1</v>
       </c>
       <c r="Z25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB25">
         <v>5</v>
       </c>
       <c r="AC25">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE25">
         <v>7</v>
       </c>
       <c r="AF25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG25">
         <v>10</v>
@@ -3172,25 +3121,25 @@
         <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q26">
         <v>-1</v>
@@ -3220,25 +3169,25 @@
         <v>-1</v>
       </c>
       <c r="Z26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC26">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AD26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE26">
         <v>8</v>
       </c>
       <c r="AF26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG26">
         <v>10</v>
@@ -3273,25 +3222,25 @@
         <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q27">
         <v>-1</v>
@@ -3321,25 +3270,25 @@
         <v>-1</v>
       </c>
       <c r="Z27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB27">
         <v>5</v>
       </c>
       <c r="AC27">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE27">
         <v>6</v>
       </c>
       <c r="AF27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG27">
         <v>10</v>
@@ -3374,25 +3323,25 @@
         <v>10</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q28">
         <v>-1</v>
@@ -3422,7 +3371,7 @@
         <v>-1</v>
       </c>
       <c r="Z28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA28">
         <v>5</v>
@@ -3475,25 +3424,25 @@
         <v>10</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q29">
         <v>-1</v>
@@ -3523,7 +3472,7 @@
         <v>-1</v>
       </c>
       <c r="Z29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA29">
         <v>10</v>
@@ -3532,16 +3481,16 @@
         <v>5</v>
       </c>
       <c r="AC29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD29">
         <v>5</v>
       </c>
       <c r="AE29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG29">
         <v>10</v>
@@ -3576,25 +3525,25 @@
         <v>10</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q30">
         <v>-1</v>
@@ -3627,22 +3576,22 @@
         <v>7</v>
       </c>
       <c r="AA30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB30">
         <v>5</v>
       </c>
       <c r="AC30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AD30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE30">
         <v>8</v>
       </c>
       <c r="AF30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG30">
         <v>10</v>
@@ -3677,25 +3626,25 @@
         <v>10</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q31">
         <v>-1</v>
@@ -3734,16 +3683,16 @@
         <v>8</v>
       </c>
       <c r="AC31">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE31">
         <v>9</v>
       </c>
       <c r="AF31">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AG31">
         <v>10</v>
@@ -3778,25 +3727,25 @@
         <v>10</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q32">
         <v>-1</v>
@@ -3832,19 +3781,19 @@
         <v>9</v>
       </c>
       <c r="AB32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC32">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AD32">
         <v>6</v>
       </c>
       <c r="AE32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG32">
         <v>10</v>
@@ -3879,25 +3828,25 @@
         <v>10</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q33">
         <v>-1</v>
@@ -3930,7 +3879,7 @@
         <v>5</v>
       </c>
       <c r="AA33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB33">
         <v>5</v>
@@ -3942,7 +3891,7 @@
         <v>5</v>
       </c>
       <c r="AE33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF33">
         <v>5</v>
@@ -3974,31 +3923,31 @@
         <v>6</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I34">
         <v>10</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q34">
         <v>-1</v>
@@ -4034,7 +3983,7 @@
         <v>5</v>
       </c>
       <c r="AB34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC34">
         <v>5</v>
@@ -4046,7 +3995,7 @@
         <v>6</v>
       </c>
       <c r="AF34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AG34">
         <v>10</v>
@@ -4081,25 +4030,25 @@
         <v>10</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q35">
         <v>-1</v>
@@ -4129,7 +4078,7 @@
         <v>-1</v>
       </c>
       <c r="Z35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA35">
         <v>5</v>
@@ -4182,25 +4131,25 @@
         <v>10</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q36">
         <v>-1</v>
@@ -4230,16 +4179,16 @@
         <v>-1</v>
       </c>
       <c r="Z36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB36">
         <v>5</v>
       </c>
       <c r="AC36">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AD36">
         <v>5</v>
@@ -4283,25 +4232,25 @@
         <v>10</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q37">
         <v>-1</v>
@@ -4337,16 +4286,16 @@
         <v>9</v>
       </c>
       <c r="AB37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF37">
         <v>7</v>
@@ -4384,25 +4333,25 @@
         <v>10</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q38">
         <v>-1</v>
@@ -4432,25 +4381,25 @@
         <v>-1</v>
       </c>
       <c r="Z38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB38">
         <v>5</v>
       </c>
       <c r="AC38">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AD38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE38">
         <v>8</v>
       </c>
       <c r="AF38">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG38">
         <v>10</v>
@@ -4485,25 +4434,25 @@
         <v>10</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q39">
         <v>-1</v>
@@ -4545,13 +4494,13 @@
         <v>5</v>
       </c>
       <c r="AD39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG39">
         <v>10</v>
@@ -4586,25 +4535,25 @@
         <v>10</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q40">
         <v>-1</v>
@@ -4640,19 +4589,19 @@
         <v>6</v>
       </c>
       <c r="AB40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC40">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AD40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG40">
         <v>10</v>
@@ -4687,25 +4636,25 @@
         <v>10</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q41">
         <v>-1</v>
@@ -4735,10 +4684,10 @@
         <v>-1</v>
       </c>
       <c r="Z41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA41">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB41">
         <v>5</v>
@@ -4747,13 +4696,13 @@
         <v>5</v>
       </c>
       <c r="AD41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE41">
         <v>7</v>
       </c>
       <c r="AF41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG41">
         <v>10</v>
@@ -4782,19 +4731,19 @@
         <v>10</v>
       </c>
       <c r="J42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q42">
         <v>-1</v>
@@ -4818,19 +4767,19 @@
         <v>-1</v>
       </c>
       <c r="Z42">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA42">
         <v>5</v>
       </c>
       <c r="AB42">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AD42">
         <v>6</v>
       </c>
       <c r="AF42">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG42">
         <v>10</v>
@@ -4865,25 +4814,25 @@
         <v>10</v>
       </c>
       <c r="J43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q43">
         <v>-1</v>
@@ -4916,22 +4865,22 @@
         <v>8</v>
       </c>
       <c r="AA43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB43">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC43">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD43">
         <v>9</v>
       </c>
       <c r="AE43">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF43">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG43">
         <v>10</v>
@@ -5100,46 +5049,46 @@
         <v>100</v>
       </c>
       <c r="J4">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="K4">
         <v>100</v>
       </c>
       <c r="L4">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="M4">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="N4">
-        <v>90</v>
+        <v>95.2</v>
       </c>
       <c r="O4">
+        <v>96.8</v>
+      </c>
+      <c r="P4">
+        <v>100</v>
+      </c>
+      <c r="Q4">
+        <v>100</v>
+      </c>
+      <c r="R4">
+        <v>85</v>
+      </c>
+      <c r="S4">
+        <v>100</v>
+      </c>
+      <c r="T4">
+        <v>85</v>
+      </c>
+      <c r="U4">
         <v>93.8</v>
       </c>
-      <c r="P4">
-        <v>100</v>
-      </c>
-      <c r="Q4">
-        <v>100</v>
-      </c>
-      <c r="R4">
-        <v>90</v>
-      </c>
-      <c r="S4">
-        <v>100</v>
-      </c>
-      <c r="T4">
-        <v>90</v>
-      </c>
-      <c r="U4">
-        <v>87.5</v>
-      </c>
       <c r="V4">
-        <v>90</v>
+        <v>95.2</v>
       </c>
       <c r="W4">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="X4">
         <v>100</v>
@@ -5177,7 +5126,7 @@
         <v>100</v>
       </c>
       <c r="J5">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K5">
         <v>100</v>
@@ -5189,20 +5138,20 @@
         <v>100</v>
       </c>
       <c r="N5">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="O5">
+        <v>90.3</v>
+      </c>
+      <c r="P5">
+        <v>100</v>
+      </c>
+      <c r="Q5">
+        <v>100</v>
+      </c>
+      <c r="R5">
         <v>95</v>
       </c>
-      <c r="O5">
-        <v>87.5</v>
-      </c>
-      <c r="P5">
-        <v>100</v>
-      </c>
-      <c r="Q5">
-        <v>100</v>
-      </c>
-      <c r="R5">
-        <v>100</v>
-      </c>
       <c r="S5">
         <v>100</v>
       </c>
@@ -5213,10 +5162,10 @@
         <v>100</v>
       </c>
       <c r="V5">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="W5">
-        <v>87.5</v>
+        <v>90.3</v>
       </c>
       <c r="X5">
         <v>100</v>
@@ -5254,22 +5203,22 @@
         <v>100</v>
       </c>
       <c r="J6">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="K6">
         <v>100</v>
       </c>
       <c r="L6">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="M6">
         <v>87.5</v>
       </c>
       <c r="N6">
-        <v>90</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="O6">
-        <v>81.3</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="P6">
         <v>100</v>
@@ -5278,22 +5227,22 @@
         <v>100</v>
       </c>
       <c r="R6">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="S6">
         <v>100</v>
       </c>
       <c r="T6">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="U6">
         <v>87.5</v>
       </c>
       <c r="V6">
-        <v>90</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="W6">
-        <v>81.3</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="X6">
         <v>100</v>
@@ -5331,22 +5280,22 @@
         <v>100</v>
       </c>
       <c r="J7">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="K7">
         <v>100</v>
       </c>
       <c r="L7">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="M7">
         <v>87.5</v>
       </c>
       <c r="N7">
-        <v>90</v>
+        <v>95.2</v>
       </c>
       <c r="O7">
-        <v>93.8</v>
+        <v>90.3</v>
       </c>
       <c r="P7">
         <v>100</v>
@@ -5355,22 +5304,22 @@
         <v>100</v>
       </c>
       <c r="R7">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="S7">
         <v>100</v>
       </c>
       <c r="T7">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="U7">
         <v>87.5</v>
       </c>
       <c r="V7">
-        <v>90</v>
+        <v>95.2</v>
       </c>
       <c r="W7">
-        <v>93.8</v>
+        <v>90.3</v>
       </c>
       <c r="X7">
         <v>100</v>
@@ -5408,7 +5357,7 @@
         <v>100</v>
       </c>
       <c r="J8">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="K8">
         <v>100</v>
@@ -5417,13 +5366,13 @@
         <v>100</v>
       </c>
       <c r="M8">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="N8">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O8">
-        <v>87.5</v>
+        <v>90.3</v>
       </c>
       <c r="P8">
         <v>100</v>
@@ -5432,7 +5381,7 @@
         <v>100</v>
       </c>
       <c r="R8">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="S8">
         <v>100</v>
@@ -5441,13 +5390,13 @@
         <v>100</v>
       </c>
       <c r="U8">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V8">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="W8">
-        <v>87.5</v>
+        <v>90.3</v>
       </c>
       <c r="X8">
         <v>100</v>
@@ -5485,7 +5434,7 @@
         <v>100</v>
       </c>
       <c r="J9">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K9">
         <v>100</v>
@@ -5500,7 +5449,7 @@
         <v>100</v>
       </c>
       <c r="O9">
-        <v>93.8</v>
+        <v>90.3</v>
       </c>
       <c r="P9">
         <v>100</v>
@@ -5509,7 +5458,7 @@
         <v>100</v>
       </c>
       <c r="R9">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="S9">
         <v>100</v>
@@ -5524,7 +5473,7 @@
         <v>100</v>
       </c>
       <c r="W9">
-        <v>93.8</v>
+        <v>90.3</v>
       </c>
       <c r="X9">
         <v>100</v>
@@ -5562,22 +5511,22 @@
         <v>100</v>
       </c>
       <c r="J10">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="K10">
         <v>100</v>
       </c>
       <c r="L10">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="M10">
-        <v>93.8</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="N10">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O10">
-        <v>81.3</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="P10">
         <v>100</v>
@@ -5586,22 +5535,22 @@
         <v>100</v>
       </c>
       <c r="R10">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="S10">
         <v>100</v>
       </c>
       <c r="T10">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="U10">
-        <v>93.8</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="V10">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="W10">
-        <v>81.3</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="X10">
         <v>100</v>
@@ -5639,22 +5588,22 @@
         <v>100</v>
       </c>
       <c r="J11">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="K11">
         <v>100</v>
       </c>
       <c r="L11">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="M11">
         <v>100</v>
       </c>
       <c r="N11">
-        <v>90</v>
+        <v>95.2</v>
       </c>
       <c r="O11">
-        <v>81.3</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="P11">
         <v>100</v>
@@ -5663,22 +5612,22 @@
         <v>100</v>
       </c>
       <c r="R11">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="S11">
         <v>100</v>
       </c>
       <c r="T11">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="U11">
         <v>100</v>
       </c>
       <c r="V11">
-        <v>90</v>
+        <v>95.2</v>
       </c>
       <c r="W11">
-        <v>81.3</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="X11">
         <v>100</v>
@@ -5716,46 +5665,46 @@
         <v>100</v>
       </c>
       <c r="J12">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="K12">
         <v>100</v>
       </c>
       <c r="L12">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="M12">
-        <v>87.5</v>
+        <v>81.3</v>
       </c>
       <c r="N12">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="O12">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="P12">
+        <v>100</v>
+      </c>
+      <c r="Q12">
+        <v>100</v>
+      </c>
+      <c r="R12">
+        <v>70</v>
+      </c>
+      <c r="S12">
+        <v>100</v>
+      </c>
+      <c r="T12">
         <v>95</v>
       </c>
-      <c r="O12">
+      <c r="U12">
         <v>81.3</v>
       </c>
-      <c r="P12">
-        <v>100</v>
-      </c>
-      <c r="Q12">
-        <v>100</v>
-      </c>
-      <c r="R12">
-        <v>80</v>
-      </c>
-      <c r="S12">
-        <v>100</v>
-      </c>
-      <c r="T12">
-        <v>90</v>
-      </c>
-      <c r="U12">
-        <v>87.5</v>
-      </c>
       <c r="V12">
-        <v>95</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="W12">
-        <v>81.3</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="X12">
         <v>100</v>
@@ -5793,7 +5742,7 @@
         <v>100</v>
       </c>
       <c r="J13">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="K13">
         <v>100</v>
@@ -5802,13 +5751,13 @@
         <v>90</v>
       </c>
       <c r="M13">
-        <v>68.8</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="N13">
         <v>100</v>
       </c>
       <c r="O13">
-        <v>81.3</v>
+        <v>90.3</v>
       </c>
       <c r="P13">
         <v>100</v>
@@ -5817,7 +5766,7 @@
         <v>100</v>
       </c>
       <c r="R13">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="S13">
         <v>100</v>
@@ -5826,13 +5775,13 @@
         <v>90</v>
       </c>
       <c r="U13">
-        <v>68.8</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="V13">
         <v>100</v>
       </c>
       <c r="W13">
-        <v>81.3</v>
+        <v>90.3</v>
       </c>
       <c r="X13">
         <v>100</v>
@@ -5870,7 +5819,7 @@
         <v>100</v>
       </c>
       <c r="J14">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="K14">
         <v>100</v>
@@ -5894,7 +5843,7 @@
         <v>100</v>
       </c>
       <c r="R14">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="S14">
         <v>100</v>
@@ -5959,7 +5908,7 @@
         <v>100</v>
       </c>
       <c r="N15">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O15">
         <v>100</v>
@@ -5983,7 +5932,7 @@
         <v>100</v>
       </c>
       <c r="V15">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="W15">
         <v>100</v>
@@ -6101,13 +6050,13 @@
         <v>100</v>
       </c>
       <c r="J17">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K17">
         <v>100</v>
       </c>
       <c r="L17">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="M17">
         <v>100</v>
@@ -6116,7 +6065,7 @@
         <v>100</v>
       </c>
       <c r="O17">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="P17">
         <v>100</v>
@@ -6125,13 +6074,13 @@
         <v>100</v>
       </c>
       <c r="R17">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="S17">
         <v>100</v>
       </c>
       <c r="T17">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="U17">
         <v>100</v>
@@ -6140,7 +6089,7 @@
         <v>100</v>
       </c>
       <c r="W17">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="X17">
         <v>100</v>
@@ -6184,16 +6133,16 @@
         <v>100</v>
       </c>
       <c r="L18">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="M18">
-        <v>62.5</v>
+        <v>75</v>
       </c>
       <c r="N18">
-        <v>90</v>
+        <v>95.2</v>
       </c>
       <c r="O18">
-        <v>68.8</v>
+        <v>67.7</v>
       </c>
       <c r="P18">
         <v>100</v>
@@ -6208,16 +6157,16 @@
         <v>100</v>
       </c>
       <c r="T18">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="U18">
-        <v>62.5</v>
+        <v>75</v>
       </c>
       <c r="V18">
-        <v>90</v>
+        <v>95.2</v>
       </c>
       <c r="W18">
-        <v>68.8</v>
+        <v>67.7</v>
       </c>
       <c r="X18">
         <v>100</v>
@@ -6255,22 +6204,22 @@
         <v>100</v>
       </c>
       <c r="J19">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="K19">
         <v>100</v>
       </c>
       <c r="L19">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="M19">
         <v>100</v>
       </c>
       <c r="N19">
-        <v>90</v>
+        <v>95.2</v>
       </c>
       <c r="O19">
-        <v>68.8</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="P19">
         <v>100</v>
@@ -6279,22 +6228,22 @@
         <v>100</v>
       </c>
       <c r="R19">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="S19">
         <v>100</v>
       </c>
       <c r="T19">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="U19">
         <v>100</v>
       </c>
       <c r="V19">
-        <v>90</v>
+        <v>95.2</v>
       </c>
       <c r="W19">
-        <v>68.8</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="X19">
         <v>100</v>
@@ -6347,7 +6296,7 @@
         <v>100</v>
       </c>
       <c r="O20">
-        <v>87.5</v>
+        <v>93.5</v>
       </c>
       <c r="P20">
         <v>100</v>
@@ -6371,7 +6320,7 @@
         <v>100</v>
       </c>
       <c r="W20">
-        <v>87.5</v>
+        <v>93.5</v>
       </c>
       <c r="X20">
         <v>100</v>
@@ -6415,7 +6364,7 @@
         <v>100</v>
       </c>
       <c r="L21">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="M21">
         <v>100</v>
@@ -6439,7 +6388,7 @@
         <v>100</v>
       </c>
       <c r="T21">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="U21">
         <v>100</v>
@@ -6486,7 +6435,7 @@
         <v>100</v>
       </c>
       <c r="J22">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="K22">
         <v>100</v>
@@ -6495,10 +6444,10 @@
         <v>90</v>
       </c>
       <c r="M22">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="N22">
-        <v>90</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="O22">
         <v>100</v>
@@ -6510,7 +6459,7 @@
         <v>100</v>
       </c>
       <c r="R22">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="S22">
         <v>100</v>
@@ -6519,10 +6468,10 @@
         <v>90</v>
       </c>
       <c r="U22">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V22">
-        <v>90</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="W22">
         <v>100</v>
@@ -6578,7 +6527,7 @@
         <v>100</v>
       </c>
       <c r="O23">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="P23">
         <v>100</v>
@@ -6602,7 +6551,7 @@
         <v>100</v>
       </c>
       <c r="W23">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="X23">
         <v>100</v>
@@ -6640,46 +6589,46 @@
         <v>100</v>
       </c>
       <c r="J24">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="K24">
         <v>100</v>
       </c>
       <c r="L24">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M24">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="N24">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="O24">
+        <v>90.3</v>
+      </c>
+      <c r="P24">
+        <v>100</v>
+      </c>
+      <c r="Q24">
+        <v>100</v>
+      </c>
+      <c r="R24">
+        <v>85</v>
+      </c>
+      <c r="S24">
+        <v>100</v>
+      </c>
+      <c r="T24">
+        <v>90</v>
+      </c>
+      <c r="U24">
         <v>93.8</v>
       </c>
-      <c r="P24">
-        <v>100</v>
-      </c>
-      <c r="Q24">
-        <v>100</v>
-      </c>
-      <c r="R24">
-        <v>100</v>
-      </c>
-      <c r="S24">
-        <v>100</v>
-      </c>
-      <c r="T24">
-        <v>100</v>
-      </c>
-      <c r="U24">
-        <v>100</v>
-      </c>
       <c r="V24">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="W24">
-        <v>93.8</v>
+        <v>90.3</v>
       </c>
       <c r="X24">
         <v>100</v>
@@ -6717,46 +6666,46 @@
         <v>100</v>
       </c>
       <c r="J25">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="K25">
         <v>100</v>
       </c>
       <c r="L25">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="M25">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="N25">
         <v>100</v>
       </c>
       <c r="O25">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="P25">
+        <v>100</v>
+      </c>
+      <c r="Q25">
+        <v>100</v>
+      </c>
+      <c r="R25">
+        <v>65</v>
+      </c>
+      <c r="S25">
+        <v>100</v>
+      </c>
+      <c r="T25">
+        <v>85</v>
+      </c>
+      <c r="U25">
         <v>93.8</v>
       </c>
-      <c r="P25">
-        <v>100</v>
-      </c>
-      <c r="Q25">
-        <v>100</v>
-      </c>
-      <c r="R25">
-        <v>60</v>
-      </c>
-      <c r="S25">
-        <v>100</v>
-      </c>
-      <c r="T25">
-        <v>90</v>
-      </c>
-      <c r="U25">
-        <v>100</v>
-      </c>
       <c r="V25">
         <v>100</v>
       </c>
       <c r="W25">
-        <v>93.8</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="X25">
         <v>100</v>
@@ -6794,22 +6743,22 @@
         <v>100</v>
       </c>
       <c r="J26">
+        <v>80</v>
+      </c>
+      <c r="K26">
+        <v>100</v>
+      </c>
+      <c r="L26">
         <v>90</v>
       </c>
-      <c r="K26">
-        <v>100</v>
-      </c>
-      <c r="L26">
-        <v>100</v>
-      </c>
       <c r="M26">
         <v>100</v>
       </c>
       <c r="N26">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O26">
-        <v>93.8</v>
+        <v>90.3</v>
       </c>
       <c r="P26">
         <v>100</v>
@@ -6818,22 +6767,22 @@
         <v>100</v>
       </c>
       <c r="R26">
+        <v>80</v>
+      </c>
+      <c r="S26">
+        <v>100</v>
+      </c>
+      <c r="T26">
         <v>90</v>
       </c>
-      <c r="S26">
-        <v>100</v>
-      </c>
-      <c r="T26">
-        <v>100</v>
-      </c>
       <c r="U26">
         <v>100</v>
       </c>
       <c r="V26">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="W26">
-        <v>93.8</v>
+        <v>90.3</v>
       </c>
       <c r="X26">
         <v>100</v>
@@ -6871,46 +6820,46 @@
         <v>100</v>
       </c>
       <c r="J27">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K27">
         <v>100</v>
       </c>
       <c r="L27">
+        <v>85</v>
+      </c>
+      <c r="M27">
+        <v>100</v>
+      </c>
+      <c r="N27">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="O27">
+        <v>93.5</v>
+      </c>
+      <c r="P27">
+        <v>100</v>
+      </c>
+      <c r="Q27">
+        <v>100</v>
+      </c>
+      <c r="R27">
         <v>90</v>
       </c>
-      <c r="M27">
-        <v>100</v>
-      </c>
-      <c r="N27">
-        <v>95</v>
-      </c>
-      <c r="O27">
-        <v>93.8</v>
-      </c>
-      <c r="P27">
-        <v>100</v>
-      </c>
-      <c r="Q27">
-        <v>100</v>
-      </c>
-      <c r="R27">
-        <v>100</v>
-      </c>
       <c r="S27">
         <v>100</v>
       </c>
       <c r="T27">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="U27">
         <v>100</v>
       </c>
       <c r="V27">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="W27">
-        <v>93.8</v>
+        <v>93.5</v>
       </c>
       <c r="X27">
         <v>100</v>
@@ -6948,22 +6897,22 @@
         <v>100</v>
       </c>
       <c r="J28">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="K28">
         <v>100</v>
       </c>
       <c r="L28">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="M28">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="N28">
-        <v>95</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="O28">
-        <v>81.3</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="P28">
         <v>100</v>
@@ -6972,22 +6921,22 @@
         <v>100</v>
       </c>
       <c r="R28">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="S28">
         <v>100</v>
       </c>
       <c r="T28">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="U28">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="V28">
-        <v>95</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="W28">
-        <v>81.3</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="X28">
         <v>100</v>
@@ -7034,10 +6983,10 @@
         <v>100</v>
       </c>
       <c r="M29">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="N29">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O29">
         <v>100</v>
@@ -7058,10 +7007,10 @@
         <v>100</v>
       </c>
       <c r="U29">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V29">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="W29">
         <v>100</v>
@@ -7108,16 +7057,16 @@
         <v>100</v>
       </c>
       <c r="L30">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="M30">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="N30">
-        <v>95</v>
+        <v>95.2</v>
       </c>
       <c r="O30">
-        <v>93.8</v>
+        <v>90.3</v>
       </c>
       <c r="P30">
         <v>100</v>
@@ -7132,16 +7081,16 @@
         <v>100</v>
       </c>
       <c r="T30">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="U30">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V30">
-        <v>95</v>
+        <v>95.2</v>
       </c>
       <c r="W30">
-        <v>93.8</v>
+        <v>90.3</v>
       </c>
       <c r="X30">
         <v>100</v>
@@ -7256,7 +7205,7 @@
         <v>100</v>
       </c>
       <c r="J32">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K32">
         <v>100</v>
@@ -7268,10 +7217,10 @@
         <v>100</v>
       </c>
       <c r="N32">
-        <v>90</v>
+        <v>90.5</v>
       </c>
       <c r="O32">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="P32">
         <v>100</v>
@@ -7280,7 +7229,7 @@
         <v>100</v>
       </c>
       <c r="R32">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="S32">
         <v>100</v>
@@ -7292,10 +7241,10 @@
         <v>100</v>
       </c>
       <c r="V32">
-        <v>90</v>
+        <v>90.5</v>
       </c>
       <c r="W32">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="X32">
         <v>100</v>
@@ -7333,22 +7282,22 @@
         <v>100</v>
       </c>
       <c r="J33">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K33">
         <v>100</v>
       </c>
       <c r="L33">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="M33">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="N33">
-        <v>90</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="O33">
-        <v>68.8</v>
+        <v>35.5</v>
       </c>
       <c r="P33">
         <v>100</v>
@@ -7357,22 +7306,22 @@
         <v>100</v>
       </c>
       <c r="R33">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="S33">
         <v>100</v>
       </c>
       <c r="T33">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="U33">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V33">
-        <v>90</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="W33">
-        <v>68.8</v>
+        <v>35.5</v>
       </c>
       <c r="X33">
         <v>100</v>
@@ -7404,55 +7353,55 @@
         <v>81.3</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I34">
         <v>100</v>
       </c>
       <c r="J34">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="K34">
         <v>100</v>
       </c>
       <c r="L34">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="M34">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="N34">
         <v>100</v>
       </c>
       <c r="O34">
-        <v>81.3</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q34">
         <v>100</v>
       </c>
       <c r="R34">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="S34">
         <v>100</v>
       </c>
       <c r="T34">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="U34">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V34">
         <v>100</v>
       </c>
       <c r="W34">
-        <v>81.3</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y34">
         <v>100</v>
@@ -7487,22 +7436,22 @@
         <v>100</v>
       </c>
       <c r="J35">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="K35">
         <v>100</v>
       </c>
       <c r="L35">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="M35">
         <v>100</v>
       </c>
       <c r="N35">
-        <v>95</v>
+        <v>95.2</v>
       </c>
       <c r="O35">
-        <v>93.8</v>
+        <v>93.5</v>
       </c>
       <c r="P35">
         <v>100</v>
@@ -7511,22 +7460,22 @@
         <v>100</v>
       </c>
       <c r="R35">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="S35">
         <v>100</v>
       </c>
       <c r="T35">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="U35">
         <v>100</v>
       </c>
       <c r="V35">
-        <v>95</v>
+        <v>95.2</v>
       </c>
       <c r="W35">
-        <v>93.8</v>
+        <v>93.5</v>
       </c>
       <c r="X35">
         <v>100</v>
@@ -7564,7 +7513,7 @@
         <v>100</v>
       </c>
       <c r="J36">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K36">
         <v>100</v>
@@ -7573,13 +7522,13 @@
         <v>80</v>
       </c>
       <c r="M36">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="N36">
-        <v>95</v>
+        <v>95.2</v>
       </c>
       <c r="O36">
-        <v>81.3</v>
+        <v>90.3</v>
       </c>
       <c r="P36">
         <v>100</v>
@@ -7588,7 +7537,7 @@
         <v>100</v>
       </c>
       <c r="R36">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="S36">
         <v>100</v>
@@ -7597,13 +7546,13 @@
         <v>80</v>
       </c>
       <c r="U36">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="V36">
-        <v>95</v>
+        <v>95.2</v>
       </c>
       <c r="W36">
-        <v>81.3</v>
+        <v>90.3</v>
       </c>
       <c r="X36">
         <v>100</v>
@@ -7641,19 +7590,19 @@
         <v>100</v>
       </c>
       <c r="J37">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K37">
         <v>100</v>
       </c>
       <c r="L37">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M37">
         <v>100</v>
       </c>
       <c r="N37">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O37">
         <v>100</v>
@@ -7665,19 +7614,19 @@
         <v>100</v>
       </c>
       <c r="R37">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S37">
         <v>100</v>
       </c>
       <c r="T37">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="U37">
         <v>100</v>
       </c>
       <c r="V37">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="W37">
         <v>100</v>
@@ -7718,43 +7667,43 @@
         <v>100</v>
       </c>
       <c r="J38">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K38">
         <v>100</v>
       </c>
       <c r="L38">
+        <v>95</v>
+      </c>
+      <c r="M38">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="N38">
+        <v>95.2</v>
+      </c>
+      <c r="O38">
+        <v>100</v>
+      </c>
+      <c r="P38">
+        <v>100</v>
+      </c>
+      <c r="Q38">
+        <v>100</v>
+      </c>
+      <c r="R38">
         <v>90</v>
       </c>
-      <c r="M38">
-        <v>93.8</v>
-      </c>
-      <c r="N38">
+      <c r="S38">
+        <v>100</v>
+      </c>
+      <c r="T38">
         <v>95</v>
       </c>
-      <c r="O38">
-        <v>100</v>
-      </c>
-      <c r="P38">
-        <v>100</v>
-      </c>
-      <c r="Q38">
-        <v>100</v>
-      </c>
-      <c r="R38">
-        <v>80</v>
-      </c>
-      <c r="S38">
-        <v>100</v>
-      </c>
-      <c r="T38">
-        <v>90</v>
-      </c>
       <c r="U38">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V38">
-        <v>95</v>
+        <v>95.2</v>
       </c>
       <c r="W38">
         <v>100</v>
@@ -7801,16 +7750,16 @@
         <v>100</v>
       </c>
       <c r="L39">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="M39">
         <v>100</v>
       </c>
       <c r="N39">
-        <v>90</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="O39">
-        <v>68.8</v>
+        <v>74.2</v>
       </c>
       <c r="P39">
         <v>100</v>
@@ -7825,16 +7774,16 @@
         <v>100</v>
       </c>
       <c r="T39">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="U39">
         <v>100</v>
       </c>
       <c r="V39">
-        <v>90</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="W39">
-        <v>68.8</v>
+        <v>74.2</v>
       </c>
       <c r="X39">
         <v>100</v>
@@ -7872,16 +7821,16 @@
         <v>100</v>
       </c>
       <c r="J40">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K40">
         <v>100</v>
       </c>
       <c r="L40">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M40">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="N40">
         <v>100</v>
@@ -7896,16 +7845,16 @@
         <v>100</v>
       </c>
       <c r="R40">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="S40">
         <v>100</v>
       </c>
       <c r="T40">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="U40">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V40">
         <v>100</v>
@@ -7949,22 +7898,22 @@
         <v>100</v>
       </c>
       <c r="J41">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="K41">
         <v>100</v>
       </c>
       <c r="L41">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="M41">
         <v>81.3</v>
       </c>
       <c r="N41">
-        <v>90</v>
+        <v>95.2</v>
       </c>
       <c r="O41">
-        <v>81.3</v>
+        <v>74.2</v>
       </c>
       <c r="P41">
         <v>100</v>
@@ -7973,22 +7922,22 @@
         <v>100</v>
       </c>
       <c r="R41">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="S41">
         <v>100</v>
       </c>
       <c r="T41">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="U41">
         <v>81.3</v>
       </c>
       <c r="V41">
-        <v>90</v>
+        <v>95.2</v>
       </c>
       <c r="W41">
-        <v>81.3</v>
+        <v>74.2</v>
       </c>
       <c r="X41">
         <v>100</v>
@@ -8026,7 +7975,7 @@
         <v>100</v>
       </c>
       <c r="L42">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="N42">
         <v>100</v>
@@ -8044,7 +7993,7 @@
         <v>100</v>
       </c>
       <c r="T42">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="V42">
         <v>100</v>
@@ -8091,7 +8040,7 @@
         <v>100</v>
       </c>
       <c r="L43">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M43">
         <v>100</v>
@@ -8115,7 +8064,7 @@
         <v>100</v>
       </c>
       <c r="T43">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="U43">
         <v>100</v>
@@ -8187,28 +8136,28 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>66</v>
       </c>
       <c r="C2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E2">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F2" s="2">
-        <v>28.2</v>
+        <v>45</v>
       </c>
       <c r="G2" s="2">
-        <v>71.8</v>
+        <v>55</v>
       </c>
       <c r="H2">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -8219,7 +8168,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>67</v>
@@ -8228,19 +8177,19 @@
         <v>40</v>
       </c>
       <c r="D3">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E3">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F3" s="2">
-        <v>42.5</v>
+        <v>60</v>
       </c>
       <c r="G3" s="2">
-        <v>57.5</v>
+        <v>40</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -8251,7 +8200,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>68</v>
@@ -8272,7 +8221,7 @@
         <v>40</v>
       </c>
       <c r="H4">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -8283,25 +8232,25 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>69</v>
       </c>
       <c r="C5">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D5">
         <v>25</v>
       </c>
       <c r="E5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F5" s="2">
-        <v>62.5</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="G5" s="2">
-        <v>37.5</v>
+        <v>35.9</v>
       </c>
       <c r="H5">
         <v>6.7</v>
@@ -8315,7 +8264,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>70</v>
@@ -8324,30 +8273,30 @@
         <v>40</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E6">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F6" s="2">
-        <v>62.5</v>
+        <v>77.5</v>
       </c>
       <c r="G6" s="2">
-        <v>35</v>
+        <v>22.5</v>
       </c>
       <c r="H6">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" s="2">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
         <v>71</v>
@@ -8356,19 +8305,19 @@
         <v>40</v>
       </c>
       <c r="D7">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F7" s="2">
-        <v>77.5</v>
+        <v>82.5</v>
       </c>
       <c r="G7" s="2">
-        <v>22.5</v>
+        <v>17.5</v>
       </c>
       <c r="H7">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -8388,19 +8337,19 @@
         <v>39</v>
       </c>
       <c r="D8">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2">
-        <v>89.7</v>
+        <v>100</v>
       </c>
       <c r="G8" s="2">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -8448,7 +8397,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -8475,26 +8424,6 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>24330051920410</v>
-      </c>
-      <c r="B2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>70</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8502,7 +8431,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -8534,22 +8463,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920304</v>
+        <v>24330051920093</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="D2" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -8557,22 +8486,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920304</v>
+        <v>24330051920093</v>
       </c>
       <c r="B3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -8580,22 +8509,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920142</v>
+        <v>24330051920122</v>
       </c>
       <c r="B4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -8603,22 +8532,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920142</v>
+        <v>24330051920122</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -8626,22 +8555,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920313</v>
+        <v>24330051920142</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -8649,22 +8578,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920313</v>
+        <v>24330051920131</v>
       </c>
       <c r="B7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -8675,19 +8604,19 @@
         <v>24330051920152</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C8" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -8695,22 +8624,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920152</v>
+        <v>24330051920303</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C9" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -8721,19 +8650,19 @@
         <v>24330051920403</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D10" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -8741,22 +8670,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920403</v>
+        <v>24330051920149</v>
       </c>
       <c r="B11" t="s">
         <v>85</v>
       </c>
       <c r="C11" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D11" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -8764,22 +8693,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920147</v>
+        <v>24330051920305</v>
       </c>
       <c r="B12" t="s">
         <v>86</v>
       </c>
       <c r="C12" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D12" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -8787,19 +8716,19 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>24330051920147</v>
+        <v>24330051920144</v>
       </c>
       <c r="B13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C13" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F13" t="s">
         <v>68</v>
@@ -8810,22 +8739,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>24330051920144</v>
+        <v>24330051920306</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="E14" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -8833,277 +8762,24 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>24330051920144</v>
+        <v>23330051920343</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D15" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>24330051920122</v>
-      </c>
-      <c r="B16" t="s">
-        <v>88</v>
-      </c>
-      <c r="C16" t="s">
-        <v>104</v>
-      </c>
-      <c r="D16" t="s">
-        <v>119</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>71</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>24330051920122</v>
-      </c>
-      <c r="B17" t="s">
-        <v>88</v>
-      </c>
-      <c r="C17" t="s">
-        <v>104</v>
-      </c>
-      <c r="D17" t="s">
-        <v>119</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>66</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>24330051920090</v>
-      </c>
-      <c r="B18" t="s">
-        <v>89</v>
-      </c>
-      <c r="C18" t="s">
-        <v>105</v>
-      </c>
-      <c r="D18" t="s">
-        <v>120</v>
-      </c>
-      <c r="E18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" t="s">
-        <v>70</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>24330051920131</v>
-      </c>
-      <c r="B19" t="s">
-        <v>90</v>
-      </c>
-      <c r="C19" t="s">
-        <v>98</v>
-      </c>
-      <c r="D19" t="s">
-        <v>121</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>66</v>
-      </c>
-      <c r="G19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>24330051920302</v>
-      </c>
-      <c r="B20" t="s">
-        <v>91</v>
-      </c>
-      <c r="C20" t="s">
-        <v>106</v>
-      </c>
-      <c r="D20" t="s">
-        <v>122</v>
-      </c>
-      <c r="E20" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" t="s">
-        <v>70</v>
-      </c>
-      <c r="G20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>24330051920303</v>
-      </c>
-      <c r="B21" t="s">
-        <v>92</v>
-      </c>
-      <c r="C21" t="s">
-        <v>107</v>
-      </c>
-      <c r="D21" t="s">
-        <v>123</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>66</v>
-      </c>
-      <c r="G21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>24330051920148</v>
-      </c>
-      <c r="B22" t="s">
-        <v>93</v>
-      </c>
-      <c r="C22" t="s">
-        <v>108</v>
-      </c>
-      <c r="D22" t="s">
-        <v>124</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>66</v>
-      </c>
-      <c r="G22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>24330051920149</v>
-      </c>
-      <c r="B23" t="s">
-        <v>93</v>
-      </c>
-      <c r="C23" t="s">
-        <v>109</v>
-      </c>
-      <c r="D23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" t="s">
-        <v>67</v>
-      </c>
-      <c r="G23">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>24330051920300</v>
-      </c>
-      <c r="B24" t="s">
-        <v>94</v>
-      </c>
-      <c r="C24" t="s">
-        <v>110</v>
-      </c>
-      <c r="D24" t="s">
-        <v>126</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>66</v>
-      </c>
-      <c r="G24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>23330051920343</v>
-      </c>
-      <c r="B25" t="s">
-        <v>95</v>
-      </c>
-      <c r="C25" t="s">
-        <v>103</v>
-      </c>
-      <c r="D25" t="s">
-        <v>127</v>
-      </c>
-      <c r="E25" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" t="s">
-        <v>69</v>
-      </c>
-      <c r="G25">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>24330051920125</v>
-      </c>
-      <c r="B26" t="s">
-        <v>96</v>
-      </c>
-      <c r="C26" t="s">
-        <v>111</v>
-      </c>
-      <c r="D26" t="s">
-        <v>128</v>
-      </c>
-      <c r="E26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26" t="s">
-        <v>69</v>
-      </c>
-      <c r="G26">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1AV - Estadisticos 20241.xlsx
+++ b/grupos/1AV - Estadisticos 20241.xlsx
@@ -236,7 +236,7 @@
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
-    <t>Hernández Mendoza Delfina</t>
+    <t>Breniz Camarillo Lysette</t>
   </si>
   <si>
     <t>Desc Desc Desc</t>

--- a/grupos/1AV - Estadisticos 20241.xlsx
+++ b/grupos/1AV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="109">
   <si>
     <t>Materia</t>
   </si>
@@ -236,12 +236,12 @@
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
+    <t>Desc Desc Desc</t>
+  </si>
+  <si>
     <t>Breniz Camarillo Lysette</t>
   </si>
   <si>
-    <t>Desc Desc Desc</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -257,9 +257,6 @@
     <t>ARIAS</t>
   </si>
   <si>
-    <t>RIOS</t>
-  </si>
-  <si>
     <t>CAMACHO</t>
   </si>
   <si>
@@ -293,9 +290,6 @@
     <t>SARMIENTO</t>
   </si>
   <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
@@ -321,9 +315,6 @@
   </si>
   <si>
     <t>URIEL ARTURO</t>
-  </si>
-  <si>
-    <t>UZIEL</t>
   </si>
   <si>
     <t>ALEXANDRO</t>
@@ -920,7 +911,7 @@
         <v>9</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -1021,7 +1012,7 @@
         <v>7</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -1122,7 +1113,7 @@
         <v>6</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -1223,7 +1214,7 @@
         <v>7</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -1324,7 +1315,7 @@
         <v>6</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -1425,7 +1416,7 @@
         <v>6</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -1526,7 +1517,7 @@
         <v>6</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -1627,7 +1618,7 @@
         <v>6</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -1728,7 +1719,7 @@
         <v>6</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -1829,7 +1820,7 @@
         <v>10</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -1930,7 +1921,7 @@
         <v>7</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -2031,7 +2022,7 @@
         <v>10</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -2132,7 +2123,7 @@
         <v>10</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -2233,7 +2224,7 @@
         <v>6</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -2334,7 +2325,7 @@
         <v>5</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -2382,7 +2373,7 @@
         <v>5</v>
       </c>
       <c r="AG18">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:33">
@@ -2435,7 +2426,7 @@
         <v>6</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -2536,7 +2527,7 @@
         <v>9</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -2637,7 +2628,7 @@
         <v>6</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -2738,7 +2729,7 @@
         <v>5</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -2839,7 +2830,7 @@
         <v>10</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>-1</v>
@@ -2940,7 +2931,7 @@
         <v>8</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -3041,7 +3032,7 @@
         <v>7</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>-1</v>
@@ -3142,7 +3133,7 @@
         <v>9</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
         <v>-1</v>
@@ -3243,7 +3234,7 @@
         <v>8</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
         <v>-1</v>
@@ -3344,7 +3335,7 @@
         <v>5</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R28">
         <v>-1</v>
@@ -3392,7 +3383,7 @@
         <v>5</v>
       </c>
       <c r="AG28">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:33">
@@ -3445,7 +3436,7 @@
         <v>8</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
         <v>-1</v>
@@ -3546,7 +3537,7 @@
         <v>8</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
         <v>-1</v>
@@ -3647,7 +3638,7 @@
         <v>10</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
         <v>-1</v>
@@ -3748,7 +3739,7 @@
         <v>7</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
         <v>-1</v>
@@ -3849,7 +3840,7 @@
         <v>5</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
         <v>-1</v>
@@ -3950,7 +3941,7 @@
         <v>7</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
         <v>-1</v>
@@ -4051,7 +4042,7 @@
         <v>6</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R35">
         <v>-1</v>
@@ -4099,7 +4090,7 @@
         <v>6</v>
       </c>
       <c r="AG35">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:33">
@@ -4152,7 +4143,7 @@
         <v>6</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R36">
         <v>-1</v>
@@ -4253,7 +4244,7 @@
         <v>7</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R37">
         <v>-1</v>
@@ -4301,7 +4292,7 @@
         <v>7</v>
       </c>
       <c r="AG37">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:33">
@@ -4354,7 +4345,7 @@
         <v>8</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R38">
         <v>-1</v>
@@ -4455,7 +4446,7 @@
         <v>7</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R39">
         <v>-1</v>
@@ -4503,7 +4494,7 @@
         <v>6</v>
       </c>
       <c r="AG39">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:33">
@@ -4556,7 +4547,7 @@
         <v>9</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R40">
         <v>-1</v>
@@ -4657,7 +4648,7 @@
         <v>8</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R41">
         <v>-1</v>
@@ -4746,7 +4737,7 @@
         <v>9</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R42">
         <v>-1</v>
@@ -4835,7 +4826,7 @@
         <v>9</v>
       </c>
       <c r="Q43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R43">
         <v>-1</v>
@@ -5147,7 +5138,7 @@
         <v>100</v>
       </c>
       <c r="Q5">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R5">
         <v>95</v>
@@ -5171,7 +5162,7 @@
         <v>100</v>
       </c>
       <c r="Y5">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -5224,7 +5215,7 @@
         <v>100</v>
       </c>
       <c r="Q6">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R6">
         <v>85</v>
@@ -5248,7 +5239,7 @@
         <v>100</v>
       </c>
       <c r="Y6">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -5301,7 +5292,7 @@
         <v>100</v>
       </c>
       <c r="Q7">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R7">
         <v>85</v>
@@ -5325,7 +5316,7 @@
         <v>100</v>
       </c>
       <c r="Y7">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -5378,7 +5369,7 @@
         <v>100</v>
       </c>
       <c r="Q8">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R8">
         <v>75</v>
@@ -5402,7 +5393,7 @@
         <v>100</v>
       </c>
       <c r="Y8">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -5455,7 +5446,7 @@
         <v>100</v>
       </c>
       <c r="Q9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R9">
         <v>95</v>
@@ -5479,7 +5470,7 @@
         <v>100</v>
       </c>
       <c r="Y9">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -5532,7 +5523,7 @@
         <v>100</v>
       </c>
       <c r="Q10">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R10">
         <v>70</v>
@@ -5556,7 +5547,7 @@
         <v>100</v>
       </c>
       <c r="Y10">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -5609,7 +5600,7 @@
         <v>100</v>
       </c>
       <c r="Q11">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R11">
         <v>80</v>
@@ -5633,7 +5624,7 @@
         <v>100</v>
       </c>
       <c r="Y11">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -5686,7 +5677,7 @@
         <v>100</v>
       </c>
       <c r="Q12">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R12">
         <v>70</v>
@@ -5710,7 +5701,7 @@
         <v>100</v>
       </c>
       <c r="Y12">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -5840,7 +5831,7 @@
         <v>100</v>
       </c>
       <c r="Q14">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R14">
         <v>85</v>
@@ -5864,7 +5855,7 @@
         <v>100</v>
       </c>
       <c r="Y14">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -6071,7 +6062,7 @@
         <v>100</v>
       </c>
       <c r="Q17">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R17">
         <v>95</v>
@@ -6095,7 +6086,7 @@
         <v>100</v>
       </c>
       <c r="Y17">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -6148,7 +6139,7 @@
         <v>100</v>
       </c>
       <c r="Q18">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R18">
         <v>60</v>
@@ -6172,7 +6163,7 @@
         <v>100</v>
       </c>
       <c r="Y18">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -6302,7 +6293,7 @@
         <v>100</v>
       </c>
       <c r="Q20">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R20">
         <v>100</v>
@@ -6326,7 +6317,7 @@
         <v>100</v>
       </c>
       <c r="Y20">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -6610,7 +6601,7 @@
         <v>100</v>
       </c>
       <c r="Q24">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R24">
         <v>85</v>
@@ -6634,7 +6625,7 @@
         <v>100</v>
       </c>
       <c r="Y24">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -6687,7 +6678,7 @@
         <v>100</v>
       </c>
       <c r="Q25">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R25">
         <v>65</v>
@@ -6711,7 +6702,7 @@
         <v>100</v>
       </c>
       <c r="Y25">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -6764,7 +6755,7 @@
         <v>100</v>
       </c>
       <c r="Q26">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R26">
         <v>80</v>
@@ -6788,7 +6779,7 @@
         <v>100</v>
       </c>
       <c r="Y26">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -6841,7 +6832,7 @@
         <v>100</v>
       </c>
       <c r="Q27">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R27">
         <v>90</v>
@@ -6865,7 +6856,7 @@
         <v>100</v>
       </c>
       <c r="Y27">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -6918,7 +6909,7 @@
         <v>100</v>
       </c>
       <c r="Q28">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R28">
         <v>50</v>
@@ -6942,7 +6933,7 @@
         <v>100</v>
       </c>
       <c r="Y28">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -7380,7 +7371,7 @@
         <v>100</v>
       </c>
       <c r="Q34">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R34">
         <v>85</v>
@@ -7404,7 +7395,7 @@
         <v>100</v>
       </c>
       <c r="Y34">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -7534,7 +7525,7 @@
         <v>100</v>
       </c>
       <c r="Q36">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R36">
         <v>90</v>
@@ -7558,7 +7549,7 @@
         <v>100</v>
       </c>
       <c r="Y36">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -7611,7 +7602,7 @@
         <v>100</v>
       </c>
       <c r="Q37">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R37">
         <v>95</v>
@@ -7635,7 +7626,7 @@
         <v>100</v>
       </c>
       <c r="Y37">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -7688,7 +7679,7 @@
         <v>100</v>
       </c>
       <c r="Q38">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R38">
         <v>90</v>
@@ -7712,7 +7703,7 @@
         <v>100</v>
       </c>
       <c r="Y38">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -7842,7 +7833,7 @@
         <v>100</v>
       </c>
       <c r="Q40">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R40">
         <v>90</v>
@@ -7866,7 +7857,7 @@
         <v>100</v>
       </c>
       <c r="Y40">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -7919,7 +7910,7 @@
         <v>100</v>
       </c>
       <c r="Q41">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R41">
         <v>70</v>
@@ -7943,7 +7934,7 @@
         <v>100</v>
       </c>
       <c r="Y41">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -7984,7 +7975,7 @@
         <v>100</v>
       </c>
       <c r="Q42">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R42">
         <v>100</v>
@@ -8002,7 +7993,7 @@
         <v>100</v>
       </c>
       <c r="Y42">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="43" spans="1:25">
@@ -8055,7 +8046,7 @@
         <v>100</v>
       </c>
       <c r="Q43">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R43">
         <v>90</v>
@@ -8079,7 +8070,7 @@
         <v>100</v>
       </c>
       <c r="Y43">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -8328,28 +8319,28 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
         <v>72</v>
       </c>
       <c r="C8">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D8">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F8" s="2">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="G8" s="2">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="H8">
-        <v>7.7</v>
+        <v>9.4</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -8360,16 +8351,16 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
         <v>73</v>
       </c>
       <c r="C9">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D9">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -8381,7 +8372,7 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>10</v>
+        <v>7.7</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -8431,7 +8422,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -8469,10 +8460,10 @@
         <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -8492,10 +8483,10 @@
         <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -8509,22 +8500,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920122</v>
+        <v>24330051920142</v>
       </c>
       <c r="B4" t="s">
         <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -8532,22 +8523,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920122</v>
+        <v>24330051920131</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -8555,22 +8546,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920142</v>
+        <v>24330051920152</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -8578,22 +8569,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920131</v>
+        <v>24330051920303</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C7" t="s">
         <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -8601,22 +8592,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920152</v>
+        <v>24330051920403</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C8" t="s">
         <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -8624,22 +8615,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920303</v>
+        <v>24330051920149</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C9" t="s">
         <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -8647,16 +8638,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920403</v>
+        <v>24330051920305</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C10" t="s">
         <v>95</v>
       </c>
       <c r="D10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
@@ -8670,22 +8661,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920149</v>
+        <v>24330051920144</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C11" t="s">
         <v>96</v>
       </c>
       <c r="D11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -8693,16 +8684,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920305</v>
+        <v>24330051920306</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C12" t="s">
         <v>97</v>
       </c>
       <c r="D12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
@@ -8716,70 +8707,24 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>24330051920144</v>
+        <v>23330051920343</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>24330051920306</v>
-      </c>
-      <c r="B14" t="s">
-        <v>88</v>
-      </c>
-      <c r="C14" t="s">
-        <v>99</v>
-      </c>
-      <c r="D14" t="s">
-        <v>110</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>66</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>23330051920343</v>
-      </c>
-      <c r="B15" t="s">
-        <v>89</v>
-      </c>
-      <c r="C15" t="s">
-        <v>98</v>
-      </c>
-      <c r="D15" t="s">
-        <v>111</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>70</v>
-      </c>
-      <c r="G15">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1AV - Estadisticos 20241.xlsx
+++ b/grupos/1AV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="142">
   <si>
     <t>Materia</t>
   </si>
@@ -254,6 +254,36 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>APARICIO</t>
+  </si>
+  <si>
+    <t>DURAN</t>
+  </si>
+  <si>
+    <t>PANZO</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>CHICO</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
     <t>ARIAS</t>
   </si>
   <si>
@@ -290,6 +320,36 @@
     <t>VILLEGAS</t>
   </si>
   <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>RAMON</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>MEZA</t>
+  </si>
+  <si>
+    <t>TLATEMOHUE</t>
+  </si>
+  <si>
+    <t>BALDERAS</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>PAYRO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
     <t>SARMIENTO</t>
   </si>
   <si>
@@ -318,6 +378,36 @@
   </si>
   <si>
     <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>VICTOR YAEL</t>
+  </si>
+  <si>
+    <t>EDWARD ALEXIS</t>
+  </si>
+  <si>
+    <t>EDILBERTO</t>
+  </si>
+  <si>
+    <t>CARLOS ANTONIO</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>YARETH</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>RAMSES</t>
+  </si>
+  <si>
+    <t>DEREK</t>
+  </si>
+  <si>
+    <t>CARLOS ARGEL</t>
   </si>
   <si>
     <t>URIEL ARTURO</t>
@@ -7551,7 +7641,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7583,16 +7673,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920093</v>
+        <v>24330051920092</v>
       </c>
       <c r="B2" t="s">
         <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -7606,22 +7696,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920093</v>
+        <v>24330051920092</v>
       </c>
       <c r="B3" t="s">
         <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D3" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -7629,22 +7719,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920122</v>
+        <v>24330051920092</v>
       </c>
       <c r="B4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7652,22 +7742,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920122</v>
+        <v>24330051920092</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="D5" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7675,22 +7765,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920142</v>
+        <v>24330051920156</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="D6" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7698,22 +7788,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920131</v>
+        <v>24330051920156</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="D7" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7721,22 +7811,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920152</v>
+        <v>24330051920156</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="D8" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -7744,16 +7834,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920303</v>
+        <v>24330051920156</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="D9" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -7767,22 +7857,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920403</v>
+        <v>24330051920410</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="D10" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -7790,22 +7880,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920149</v>
+        <v>24330051920410</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="D11" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -7813,22 +7903,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920305</v>
+        <v>24330051920410</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D12" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -7836,22 +7926,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>24330051920144</v>
+        <v>24330051920410</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C13" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D13" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -7859,22 +7949,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>24330051920306</v>
+        <v>24330051920143</v>
       </c>
       <c r="B14" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D14" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -7882,24 +7972,806 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
+        <v>24330051920143</v>
+      </c>
+      <c r="B15" t="s">
+        <v>81</v>
+      </c>
+      <c r="C15" t="s">
+        <v>103</v>
+      </c>
+      <c r="D15" t="s">
+        <v>123</v>
+      </c>
+      <c r="E15" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" t="s">
+        <v>66</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>24330051920143</v>
+      </c>
+      <c r="B16" t="s">
+        <v>81</v>
+      </c>
+      <c r="C16" t="s">
+        <v>103</v>
+      </c>
+      <c r="D16" t="s">
+        <v>123</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>69</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>24330051920143</v>
+      </c>
+      <c r="B17" t="s">
+        <v>81</v>
+      </c>
+      <c r="C17" t="s">
+        <v>103</v>
+      </c>
+      <c r="D17" t="s">
+        <v>123</v>
+      </c>
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" t="s">
+        <v>67</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>24330051920127</v>
+      </c>
+      <c r="B18" t="s">
+        <v>82</v>
+      </c>
+      <c r="C18" t="s">
+        <v>104</v>
+      </c>
+      <c r="D18" t="s">
+        <v>124</v>
+      </c>
+      <c r="E18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F18" t="s">
+        <v>70</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>24330051920127</v>
+      </c>
+      <c r="B19" t="s">
+        <v>82</v>
+      </c>
+      <c r="C19" t="s">
+        <v>104</v>
+      </c>
+      <c r="D19" t="s">
+        <v>124</v>
+      </c>
+      <c r="E19" t="s">
+        <v>7</v>
+      </c>
+      <c r="F19" t="s">
+        <v>66</v>
+      </c>
+      <c r="G19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>24330051920127</v>
+      </c>
+      <c r="B20" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" t="s">
+        <v>104</v>
+      </c>
+      <c r="D20" t="s">
+        <v>124</v>
+      </c>
+      <c r="E20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" t="s">
+        <v>67</v>
+      </c>
+      <c r="G20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>24330051920098</v>
+      </c>
+      <c r="B21" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" t="s">
+        <v>105</v>
+      </c>
+      <c r="D21" t="s">
+        <v>125</v>
+      </c>
+      <c r="E21" t="s">
+        <v>7</v>
+      </c>
+      <c r="F21" t="s">
+        <v>66</v>
+      </c>
+      <c r="G21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>24330051920098</v>
+      </c>
+      <c r="B22" t="s">
+        <v>83</v>
+      </c>
+      <c r="C22" t="s">
+        <v>105</v>
+      </c>
+      <c r="D22" t="s">
+        <v>125</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>69</v>
+      </c>
+      <c r="G22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>24330051920098</v>
+      </c>
+      <c r="B23" t="s">
+        <v>83</v>
+      </c>
+      <c r="C23" t="s">
+        <v>105</v>
+      </c>
+      <c r="D23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E23" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" t="s">
+        <v>71</v>
+      </c>
+      <c r="G23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>24330051920155</v>
+      </c>
+      <c r="B24" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24" t="s">
+        <v>106</v>
+      </c>
+      <c r="D24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E24" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" t="s">
+        <v>68</v>
+      </c>
+      <c r="G24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>24330051920155</v>
+      </c>
+      <c r="B25" t="s">
+        <v>84</v>
+      </c>
+      <c r="C25" t="s">
+        <v>106</v>
+      </c>
+      <c r="D25" t="s">
+        <v>126</v>
+      </c>
+      <c r="E25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F25" t="s">
+        <v>66</v>
+      </c>
+      <c r="G25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>24330051920155</v>
+      </c>
+      <c r="B26" t="s">
+        <v>84</v>
+      </c>
+      <c r="C26" t="s">
+        <v>106</v>
+      </c>
+      <c r="D26" t="s">
+        <v>126</v>
+      </c>
+      <c r="E26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" t="s">
+        <v>69</v>
+      </c>
+      <c r="G26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>24330051920147</v>
+      </c>
+      <c r="B27" t="s">
+        <v>85</v>
+      </c>
+      <c r="C27" t="s">
+        <v>107</v>
+      </c>
+      <c r="D27" t="s">
+        <v>127</v>
+      </c>
+      <c r="E27" t="s">
+        <v>5</v>
+      </c>
+      <c r="F27" t="s">
+        <v>68</v>
+      </c>
+      <c r="G27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>24330051920147</v>
+      </c>
+      <c r="B28" t="s">
+        <v>85</v>
+      </c>
+      <c r="C28" t="s">
+        <v>107</v>
+      </c>
+      <c r="D28" t="s">
+        <v>127</v>
+      </c>
+      <c r="E28" t="s">
+        <v>7</v>
+      </c>
+      <c r="F28" t="s">
+        <v>66</v>
+      </c>
+      <c r="G28">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>24330051920147</v>
+      </c>
+      <c r="B29" t="s">
+        <v>85</v>
+      </c>
+      <c r="C29" t="s">
+        <v>107</v>
+      </c>
+      <c r="D29" t="s">
+        <v>127</v>
+      </c>
+      <c r="E29" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" t="s">
+        <v>67</v>
+      </c>
+      <c r="G29">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>24330051920113</v>
+      </c>
+      <c r="B30" t="s">
+        <v>86</v>
+      </c>
+      <c r="C30" t="s">
+        <v>108</v>
+      </c>
+      <c r="D30" t="s">
+        <v>128</v>
+      </c>
+      <c r="E30" t="s">
+        <v>5</v>
+      </c>
+      <c r="F30" t="s">
+        <v>68</v>
+      </c>
+      <c r="G30">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>24330051920113</v>
+      </c>
+      <c r="B31" t="s">
+        <v>86</v>
+      </c>
+      <c r="C31" t="s">
+        <v>108</v>
+      </c>
+      <c r="D31" t="s">
+        <v>128</v>
+      </c>
+      <c r="E31" t="s">
+        <v>7</v>
+      </c>
+      <c r="F31" t="s">
+        <v>66</v>
+      </c>
+      <c r="G31">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>24330051920113</v>
+      </c>
+      <c r="B32" t="s">
+        <v>86</v>
+      </c>
+      <c r="C32" t="s">
+        <v>108</v>
+      </c>
+      <c r="D32" t="s">
+        <v>128</v>
+      </c>
+      <c r="E32" t="s">
+        <v>9</v>
+      </c>
+      <c r="F32" t="s">
+        <v>67</v>
+      </c>
+      <c r="G32">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>24330051920315</v>
+      </c>
+      <c r="B33" t="s">
+        <v>87</v>
+      </c>
+      <c r="C33" t="s">
+        <v>109</v>
+      </c>
+      <c r="D33" t="s">
+        <v>129</v>
+      </c>
+      <c r="E33" t="s">
+        <v>5</v>
+      </c>
+      <c r="F33" t="s">
+        <v>68</v>
+      </c>
+      <c r="G33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>24330051920315</v>
+      </c>
+      <c r="B34" t="s">
+        <v>87</v>
+      </c>
+      <c r="C34" t="s">
+        <v>109</v>
+      </c>
+      <c r="D34" t="s">
+        <v>129</v>
+      </c>
+      <c r="E34" t="s">
+        <v>7</v>
+      </c>
+      <c r="F34" t="s">
+        <v>66</v>
+      </c>
+      <c r="G34">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>24330051920315</v>
+      </c>
+      <c r="B35" t="s">
+        <v>87</v>
+      </c>
+      <c r="C35" t="s">
+        <v>109</v>
+      </c>
+      <c r="D35" t="s">
+        <v>129</v>
+      </c>
+      <c r="E35" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" t="s">
+        <v>69</v>
+      </c>
+      <c r="G35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>24330051920093</v>
+      </c>
+      <c r="B36" t="s">
+        <v>88</v>
+      </c>
+      <c r="C36" t="s">
+        <v>110</v>
+      </c>
+      <c r="D36" t="s">
+        <v>130</v>
+      </c>
+      <c r="E36" t="s">
+        <v>7</v>
+      </c>
+      <c r="F36" t="s">
+        <v>66</v>
+      </c>
+      <c r="G36">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37">
+        <v>24330051920093</v>
+      </c>
+      <c r="B37" t="s">
+        <v>88</v>
+      </c>
+      <c r="C37" t="s">
+        <v>110</v>
+      </c>
+      <c r="D37" t="s">
+        <v>130</v>
+      </c>
+      <c r="E37" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" t="s">
+        <v>67</v>
+      </c>
+      <c r="G37">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
+        <v>24330051920122</v>
+      </c>
+      <c r="B38" t="s">
+        <v>89</v>
+      </c>
+      <c r="C38" t="s">
+        <v>111</v>
+      </c>
+      <c r="D38" t="s">
+        <v>131</v>
+      </c>
+      <c r="E38" t="s">
+        <v>5</v>
+      </c>
+      <c r="F38" t="s">
+        <v>68</v>
+      </c>
+      <c r="G38">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39">
+        <v>24330051920122</v>
+      </c>
+      <c r="B39" t="s">
+        <v>89</v>
+      </c>
+      <c r="C39" t="s">
+        <v>111</v>
+      </c>
+      <c r="D39" t="s">
+        <v>131</v>
+      </c>
+      <c r="E39" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39" t="s">
+        <v>67</v>
+      </c>
+      <c r="G39">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40">
+        <v>24330051920142</v>
+      </c>
+      <c r="B40" t="s">
+        <v>90</v>
+      </c>
+      <c r="C40" t="s">
+        <v>112</v>
+      </c>
+      <c r="D40" t="s">
+        <v>132</v>
+      </c>
+      <c r="E40" t="s">
+        <v>7</v>
+      </c>
+      <c r="F40" t="s">
+        <v>66</v>
+      </c>
+      <c r="G40">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41">
+        <v>24330051920131</v>
+      </c>
+      <c r="B41" t="s">
+        <v>91</v>
+      </c>
+      <c r="C41" t="s">
+        <v>112</v>
+      </c>
+      <c r="D41" t="s">
+        <v>133</v>
+      </c>
+      <c r="E41" t="s">
+        <v>5</v>
+      </c>
+      <c r="F41" t="s">
+        <v>68</v>
+      </c>
+      <c r="G41">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42">
+        <v>24330051920152</v>
+      </c>
+      <c r="B42" t="s">
+        <v>92</v>
+      </c>
+      <c r="C42" t="s">
+        <v>113</v>
+      </c>
+      <c r="D42" t="s">
+        <v>134</v>
+      </c>
+      <c r="E42" t="s">
+        <v>6</v>
+      </c>
+      <c r="F42" t="s">
+        <v>70</v>
+      </c>
+      <c r="G42">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43">
+        <v>24330051920303</v>
+      </c>
+      <c r="B43" t="s">
+        <v>93</v>
+      </c>
+      <c r="C43" t="s">
+        <v>114</v>
+      </c>
+      <c r="D43" t="s">
+        <v>135</v>
+      </c>
+      <c r="E43" t="s">
+        <v>9</v>
+      </c>
+      <c r="F43" t="s">
+        <v>67</v>
+      </c>
+      <c r="G43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44">
+        <v>24330051920403</v>
+      </c>
+      <c r="B44" t="s">
+        <v>94</v>
+      </c>
+      <c r="C44" t="s">
+        <v>115</v>
+      </c>
+      <c r="D44" t="s">
+        <v>136</v>
+      </c>
+      <c r="E44" t="s">
+        <v>7</v>
+      </c>
+      <c r="F44" t="s">
+        <v>66</v>
+      </c>
+      <c r="G44">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45">
+        <v>24330051920149</v>
+      </c>
+      <c r="B45" t="s">
+        <v>95</v>
+      </c>
+      <c r="C45" t="s">
+        <v>116</v>
+      </c>
+      <c r="D45" t="s">
+        <v>137</v>
+      </c>
+      <c r="E45" t="s">
+        <v>7</v>
+      </c>
+      <c r="F45" t="s">
+        <v>66</v>
+      </c>
+      <c r="G45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46">
+        <v>24330051920305</v>
+      </c>
+      <c r="B46" t="s">
+        <v>96</v>
+      </c>
+      <c r="C46" t="s">
+        <v>117</v>
+      </c>
+      <c r="D46" t="s">
+        <v>138</v>
+      </c>
+      <c r="E46" t="s">
+        <v>7</v>
+      </c>
+      <c r="F46" t="s">
+        <v>66</v>
+      </c>
+      <c r="G46">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47">
+        <v>24330051920144</v>
+      </c>
+      <c r="B47" t="s">
+        <v>97</v>
+      </c>
+      <c r="C47" t="s">
+        <v>118</v>
+      </c>
+      <c r="D47" t="s">
+        <v>139</v>
+      </c>
+      <c r="E47" t="s">
+        <v>5</v>
+      </c>
+      <c r="F47" t="s">
+        <v>68</v>
+      </c>
+      <c r="G47">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48">
+        <v>24330051920306</v>
+      </c>
+      <c r="B48" t="s">
+        <v>98</v>
+      </c>
+      <c r="C48" t="s">
+        <v>119</v>
+      </c>
+      <c r="D48" t="s">
+        <v>140</v>
+      </c>
+      <c r="E48" t="s">
+        <v>7</v>
+      </c>
+      <c r="F48" t="s">
+        <v>66</v>
+      </c>
+      <c r="G48">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49">
         <v>23330051920343</v>
       </c>
-      <c r="B15" t="s">
-        <v>89</v>
-      </c>
-      <c r="C15" t="s">
-        <v>98</v>
-      </c>
-      <c r="D15" t="s">
-        <v>111</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="B49" t="s">
+        <v>99</v>
+      </c>
+      <c r="C49" t="s">
+        <v>118</v>
+      </c>
+      <c r="D49" t="s">
+        <v>141</v>
+      </c>
+      <c r="E49" t="s">
+        <v>6</v>
+      </c>
+      <c r="F49" t="s">
         <v>70</v>
       </c>
-      <c r="G15">
+      <c r="G49">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1AV - Estadisticos 20241.xlsx
+++ b/grupos/1AV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="146">
   <si>
     <t>Materia</t>
   </si>
@@ -221,21 +221,21 @@
     <t>Valerio González Valeria</t>
   </si>
   <si>
+    <t>Silva Villegas Mario</t>
+  </si>
+  <si>
+    <t>Domínguez Burgos Marioscar</t>
+  </si>
+  <si>
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
-    <t>Silva Villegas Mario</t>
-  </si>
-  <si>
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
-    <t>Domínguez Burgos Marioscar</t>
-  </si>
-  <si>
     <t>Breniz Camarillo Lysette</t>
   </si>
   <si>
@@ -254,196 +254,208 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>DELGADO</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>DURAN</t>
+  </si>
+  <si>
     <t>APARICIO</t>
   </si>
   <si>
-    <t>DURAN</t>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>CHICO</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>CAMACHO</t>
+  </si>
+  <si>
+    <t>CHONCOA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>MORALES</t>
   </si>
   <si>
     <t>PANZO</t>
   </si>
   <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>CHICO</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
     <t>RIOS</t>
   </si>
   <si>
-    <t>CAMACHO</t>
-  </si>
-  <si>
-    <t>CHONCOA</t>
-  </si>
-  <si>
-    <t>FERNANDEZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
     <t>ROJAS</t>
   </si>
   <si>
-    <t>VILLEGAS</t>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>RAMON</t>
   </si>
   <si>
     <t>OFICIAL</t>
   </si>
   <si>
-    <t>RAMON</t>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>BALDERAS</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>PAYRO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>MEZA</t>
+  </si>
+  <si>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>TLATEMOHUE</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>CUAHUA</t>
+  </si>
+  <si>
+    <t>CORONA</t>
   </si>
   <si>
     <t>COLOHUA</t>
   </si>
   <si>
-    <t>MEZA</t>
-  </si>
-  <si>
-    <t>TLATEMOHUE</t>
-  </si>
-  <si>
-    <t>BALDERAS</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>PAYRO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
     <t>ZEPAHUA</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>CUAHUA</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
     <t>GUTIERREZ</t>
   </si>
   <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>MARIA ESTEFANIA</t>
+  </si>
+  <si>
+    <t>ERWIN ISRAEL</t>
+  </si>
+  <si>
+    <t>EDWARD ALEXIS</t>
+  </si>
+  <si>
     <t>VICTOR YAEL</t>
   </si>
   <si>
-    <t>EDWARD ALEXIS</t>
+    <t>LEVI SANTIAGO</t>
+  </si>
+  <si>
+    <t>YARETH</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>RAMSES</t>
+  </si>
+  <si>
+    <t>MIRANDA ALIZEET</t>
+  </si>
+  <si>
+    <t>DEREK</t>
+  </si>
+  <si>
+    <t>CARLOS ANTONIO</t>
+  </si>
+  <si>
+    <t>CARLOS ARGEL</t>
+  </si>
+  <si>
+    <t>URIEL ARTURO</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>ALEXANDRO</t>
+  </si>
+  <si>
+    <t>EMMANUEL GUADALUPE</t>
+  </si>
+  <si>
+    <t>BRYANA</t>
+  </si>
+  <si>
+    <t>BRAYAN</t>
+  </si>
+  <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>JOSE ABEL</t>
   </si>
   <si>
     <t>EDILBERTO</t>
   </si>
   <si>
-    <t>CARLOS ANTONIO</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>YARETH</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>RAMSES</t>
-  </si>
-  <si>
-    <t>DEREK</t>
-  </si>
-  <si>
-    <t>CARLOS ARGEL</t>
-  </si>
-  <si>
-    <t>URIEL ARTURO</t>
-  </si>
-  <si>
     <t>UZIEL</t>
   </si>
   <si>
-    <t>ALEXANDRO</t>
-  </si>
-  <si>
-    <t>EMMANUEL GUADALUPE</t>
-  </si>
-  <si>
-    <t>CRISTAL</t>
-  </si>
-  <si>
-    <t>ADOLFO</t>
-  </si>
-  <si>
-    <t>BRYANA</t>
-  </si>
-  <si>
-    <t>BRAYAN</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>JOSE ABEL</t>
-  </si>
-  <si>
     <t>LUIS ROBERTO</t>
-  </si>
-  <si>
-    <t>MAURICIO</t>
   </si>
 </sst>
 </file>
@@ -994,16 +1006,16 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
         <v>-1</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U4">
         <v>-1</v>
@@ -1015,7 +1027,7 @@
         <v>6</v>
       </c>
       <c r="X4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y4">
         <v>5</v>
@@ -1024,7 +1036,7 @@
         <v>8</v>
       </c>
       <c r="AA4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB4">
         <v>7</v>
@@ -1083,16 +1095,16 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R5">
         <v>-1</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U5">
         <v>-1</v>
@@ -1172,16 +1184,16 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R6">
         <v>-1</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U6">
         <v>-1</v>
@@ -1199,10 +1211,10 @@
         <v>5</v>
       </c>
       <c r="Z6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB6">
         <v>6</v>
@@ -1261,16 +1273,16 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R7">
         <v>-1</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U7">
         <v>-1</v>
@@ -1282,16 +1294,16 @@
         <v>7</v>
       </c>
       <c r="X7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y7">
         <v>5</v>
       </c>
       <c r="Z7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB7">
         <v>6</v>
@@ -1350,16 +1362,16 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R8">
         <v>-1</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U8">
         <v>-1</v>
@@ -1371,7 +1383,7 @@
         <v>7</v>
       </c>
       <c r="X8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y8">
         <v>6</v>
@@ -1439,16 +1451,16 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R9">
         <v>-1</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U9">
         <v>-1</v>
@@ -1469,7 +1481,7 @@
         <v>8</v>
       </c>
       <c r="AA9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB9">
         <v>9</v>
@@ -1528,16 +1540,16 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R10">
         <v>-1</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U10">
         <v>-1</v>
@@ -1617,16 +1629,16 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R11">
         <v>-1</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U11">
         <v>-1</v>
@@ -1638,16 +1650,16 @@
         <v>5</v>
       </c>
       <c r="X11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y11">
         <v>5</v>
       </c>
       <c r="Z11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB11">
         <v>8</v>
@@ -1706,16 +1718,16 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R12">
         <v>-1</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U12">
         <v>-1</v>
@@ -1733,7 +1745,7 @@
         <v>5</v>
       </c>
       <c r="Z12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA12">
         <v>6</v>
@@ -1795,16 +1807,16 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R13">
         <v>-1</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U13">
         <v>-1</v>
@@ -1822,7 +1834,7 @@
         <v>6</v>
       </c>
       <c r="Z13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA13">
         <v>8</v>
@@ -1884,16 +1896,16 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R14">
         <v>-1</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U14">
         <v>-1</v>
@@ -1914,7 +1926,7 @@
         <v>9</v>
       </c>
       <c r="AA14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB14">
         <v>9</v>
@@ -1946,7 +1958,7 @@
         <v>10</v>
       </c>
       <c r="H15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I15">
         <v>9</v>
@@ -1973,16 +1985,16 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R15">
         <v>-1</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U15">
         <v>-1</v>
@@ -2062,16 +2074,16 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
         <v>-1</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U16">
         <v>-1</v>
@@ -2083,13 +2095,13 @@
         <v>8</v>
       </c>
       <c r="X16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y16">
         <v>8</v>
       </c>
       <c r="Z16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA16">
         <v>9</v>
@@ -2151,16 +2163,16 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R17">
         <v>-1</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U17">
         <v>-1</v>
@@ -2178,7 +2190,7 @@
         <v>5</v>
       </c>
       <c r="Z17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA17">
         <v>6</v>
@@ -2240,16 +2252,16 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R18">
         <v>-1</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U18">
         <v>-1</v>
@@ -2261,7 +2273,7 @@
         <v>5</v>
       </c>
       <c r="X18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y18">
         <v>5</v>
@@ -2329,16 +2341,16 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R19">
         <v>-1</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U19">
         <v>-1</v>
@@ -2356,7 +2368,7 @@
         <v>5</v>
       </c>
       <c r="Z19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA19">
         <v>5</v>
@@ -2418,16 +2430,16 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R20">
         <v>-1</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U20">
         <v>-1</v>
@@ -2448,7 +2460,7 @@
         <v>9</v>
       </c>
       <c r="AA20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB20">
         <v>8</v>
@@ -2507,16 +2519,16 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R21">
         <v>-1</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U21">
         <v>-1</v>
@@ -2528,7 +2540,7 @@
         <v>7</v>
       </c>
       <c r="X21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y21">
         <v>6</v>
@@ -2596,16 +2608,16 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R22">
         <v>-1</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U22">
         <v>-1</v>
@@ -2617,13 +2629,13 @@
         <v>5</v>
       </c>
       <c r="X22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y22">
         <v>5</v>
       </c>
       <c r="Z22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA22">
         <v>5</v>
@@ -2685,16 +2697,16 @@
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R23">
         <v>-1</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U23">
         <v>-1</v>
@@ -2706,7 +2718,7 @@
         <v>8</v>
       </c>
       <c r="X23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y23">
         <v>7</v>
@@ -2774,16 +2786,16 @@
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R24">
         <v>-1</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U24">
         <v>-1</v>
@@ -2795,16 +2807,16 @@
         <v>7</v>
       </c>
       <c r="X24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y24">
         <v>6</v>
       </c>
       <c r="Z24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB24">
         <v>6</v>
@@ -2863,16 +2875,16 @@
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R25">
         <v>-1</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U25">
         <v>-1</v>
@@ -2890,10 +2902,10 @@
         <v>5</v>
       </c>
       <c r="Z25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB25">
         <v>7</v>
@@ -2952,16 +2964,16 @@
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R26">
         <v>-1</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U26">
         <v>-1</v>
@@ -2973,7 +2985,7 @@
         <v>7</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y26">
         <v>6</v>
@@ -3041,16 +3053,16 @@
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R27">
         <v>-1</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U27">
         <v>-1</v>
@@ -3068,10 +3080,10 @@
         <v>5</v>
       </c>
       <c r="Z27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB27">
         <v>6</v>
@@ -3130,16 +3142,16 @@
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R28">
         <v>-1</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U28">
         <v>-1</v>
@@ -3219,16 +3231,16 @@
         <v>-1</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R29">
         <v>-1</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U29">
         <v>-1</v>
@@ -3240,7 +3252,7 @@
         <v>5</v>
       </c>
       <c r="X29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y29">
         <v>5</v>
@@ -3249,7 +3261,7 @@
         <v>8</v>
       </c>
       <c r="AA29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB29">
         <v>9</v>
@@ -3308,16 +3320,16 @@
         <v>-1</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R30">
         <v>-1</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U30">
         <v>-1</v>
@@ -3335,7 +3347,7 @@
         <v>5</v>
       </c>
       <c r="Z30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA30">
         <v>6</v>
@@ -3397,16 +3409,16 @@
         <v>-1</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R31">
         <v>-1</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U31">
         <v>-1</v>
@@ -3486,16 +3498,16 @@
         <v>-1</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R32">
         <v>-1</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U32">
         <v>-1</v>
@@ -3507,7 +3519,7 @@
         <v>5</v>
       </c>
       <c r="X32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y32">
         <v>8</v>
@@ -3575,16 +3587,16 @@
         <v>-1</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R33">
         <v>-1</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U33">
         <v>-1</v>
@@ -3602,7 +3614,7 @@
         <v>5</v>
       </c>
       <c r="Z33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA33">
         <v>5</v>
@@ -3664,16 +3676,16 @@
         <v>-1</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R34">
         <v>-1</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U34">
         <v>-1</v>
@@ -3685,16 +3697,16 @@
         <v>5</v>
       </c>
       <c r="X34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y34">
         <v>6</v>
       </c>
       <c r="Z34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB34">
         <v>6</v>
@@ -3753,16 +3765,16 @@
         <v>-1</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R35">
         <v>-1</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U35">
         <v>-1</v>
@@ -3774,16 +3786,16 @@
         <v>5</v>
       </c>
       <c r="X35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y35">
         <v>5</v>
       </c>
       <c r="Z35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB35">
         <v>8</v>
@@ -3842,16 +3854,16 @@
         <v>-1</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R36">
         <v>-1</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U36">
         <v>-1</v>
@@ -3872,7 +3884,7 @@
         <v>7</v>
       </c>
       <c r="AA36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB36">
         <v>6</v>
@@ -3931,16 +3943,16 @@
         <v>-1</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R37">
         <v>-1</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U37">
         <v>-1</v>
@@ -3958,10 +3970,10 @@
         <v>6</v>
       </c>
       <c r="Z37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB37">
         <v>9</v>
@@ -4020,16 +4032,16 @@
         <v>-1</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R38">
         <v>-1</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U38">
         <v>-1</v>
@@ -4041,7 +4053,7 @@
         <v>7</v>
       </c>
       <c r="X38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y38">
         <v>5</v>
@@ -4050,7 +4062,7 @@
         <v>8</v>
       </c>
       <c r="AA38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB38">
         <v>8</v>
@@ -4109,16 +4121,16 @@
         <v>-1</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R39">
         <v>-1</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U39">
         <v>-1</v>
@@ -4130,16 +4142,16 @@
         <v>5</v>
       </c>
       <c r="X39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y39">
         <v>5</v>
       </c>
       <c r="Z39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB39">
         <v>6</v>
@@ -4198,16 +4210,16 @@
         <v>-1</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R40">
         <v>-1</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U40">
         <v>-1</v>
@@ -4225,7 +4237,7 @@
         <v>7</v>
       </c>
       <c r="Z40">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA40">
         <v>7</v>
@@ -4287,16 +4299,16 @@
         <v>-1</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R41">
         <v>-1</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U41">
         <v>-1</v>
@@ -4308,13 +4320,13 @@
         <v>5</v>
       </c>
       <c r="X41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y41">
         <v>5</v>
       </c>
       <c r="Z41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA41">
         <v>6</v>
@@ -4364,13 +4376,13 @@
         <v>-1</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R42">
         <v>-1</v>
       </c>
       <c r="T42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V42">
         <v>-1</v>
@@ -4379,13 +4391,13 @@
         <v>8</v>
       </c>
       <c r="X42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y42">
         <v>7</v>
       </c>
       <c r="AA42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC42">
         <v>8</v>
@@ -4441,16 +4453,16 @@
         <v>-1</v>
       </c>
       <c r="Q43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R43">
         <v>-1</v>
       </c>
       <c r="S43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U43">
         <v>-1</v>
@@ -4658,10 +4670,10 @@
         <v>85</v>
       </c>
       <c r="S4">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="T4">
-        <v>95.2</v>
+        <v>96.8</v>
       </c>
       <c r="U4">
         <v>96.8</v>
@@ -4729,7 +4741,7 @@
         <v>100</v>
       </c>
       <c r="T5">
-        <v>97.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="U5">
         <v>90.3</v>
@@ -4794,10 +4806,10 @@
         <v>85</v>
       </c>
       <c r="S6">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="T6">
-        <v>92.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="U6">
         <v>83.90000000000001</v>
@@ -4862,10 +4874,10 @@
         <v>85</v>
       </c>
       <c r="S7">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="T7">
-        <v>95.2</v>
+        <v>96.8</v>
       </c>
       <c r="U7">
         <v>90.3</v>
@@ -4930,10 +4942,10 @@
         <v>100</v>
       </c>
       <c r="S8">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T8">
-        <v>97.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="U8">
         <v>90.3</v>
@@ -5066,10 +5078,10 @@
         <v>85</v>
       </c>
       <c r="S10">
-        <v>78.09999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="T10">
-        <v>97.59999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="U10">
         <v>83.90000000000001</v>
@@ -5137,7 +5149,7 @@
         <v>100</v>
       </c>
       <c r="T11">
-        <v>95.2</v>
+        <v>96.8</v>
       </c>
       <c r="U11">
         <v>87.09999999999999</v>
@@ -5202,10 +5214,10 @@
         <v>95</v>
       </c>
       <c r="S12">
-        <v>81.3</v>
+        <v>87.5</v>
       </c>
       <c r="T12">
-        <v>92.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="U12">
         <v>77.40000000000001</v>
@@ -5270,7 +5282,7 @@
         <v>90</v>
       </c>
       <c r="S13">
-        <v>84.40000000000001</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="T13">
         <v>100</v>
@@ -5409,7 +5421,7 @@
         <v>100</v>
       </c>
       <c r="T15">
-        <v>97.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="U15">
         <v>100</v>
@@ -5610,10 +5622,10 @@
         <v>85</v>
       </c>
       <c r="S18">
-        <v>75</v>
+        <v>83.3</v>
       </c>
       <c r="T18">
-        <v>95.2</v>
+        <v>96.8</v>
       </c>
       <c r="U18">
         <v>67.7</v>
@@ -5681,7 +5693,7 @@
         <v>100</v>
       </c>
       <c r="T19">
-        <v>95.2</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="U19">
         <v>80.59999999999999</v>
@@ -5882,10 +5894,10 @@
         <v>90</v>
       </c>
       <c r="S22">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T22">
-        <v>92.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="U22">
         <v>100</v>
@@ -6018,10 +6030,10 @@
         <v>90</v>
       </c>
       <c r="S24">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="T24">
-        <v>95.2</v>
+        <v>96.8</v>
       </c>
       <c r="U24">
         <v>90.3</v>
@@ -6086,7 +6098,7 @@
         <v>85</v>
       </c>
       <c r="S25">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="T25">
         <v>100</v>
@@ -6157,7 +6169,7 @@
         <v>100</v>
       </c>
       <c r="T26">
-        <v>97.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="U26">
         <v>90.3</v>
@@ -6225,7 +6237,7 @@
         <v>100</v>
       </c>
       <c r="T27">
-        <v>97.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="U27">
         <v>93.5</v>
@@ -6290,10 +6302,10 @@
         <v>85</v>
       </c>
       <c r="S28">
-        <v>62.5</v>
+        <v>75</v>
       </c>
       <c r="T28">
-        <v>92.90000000000001</v>
+        <v>62.9</v>
       </c>
       <c r="U28">
         <v>77.40000000000001</v>
@@ -6358,10 +6370,10 @@
         <v>100</v>
       </c>
       <c r="S29">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T29">
-        <v>97.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="U29">
         <v>100</v>
@@ -6426,10 +6438,10 @@
         <v>92.5</v>
       </c>
       <c r="S30">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T30">
-        <v>95.2</v>
+        <v>96.8</v>
       </c>
       <c r="U30">
         <v>90.3</v>
@@ -6565,7 +6577,7 @@
         <v>100</v>
       </c>
       <c r="T32">
-        <v>90.5</v>
+        <v>93.5</v>
       </c>
       <c r="U32">
         <v>96.8</v>
@@ -6630,10 +6642,10 @@
         <v>85</v>
       </c>
       <c r="S33">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T33">
-        <v>92.90000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="U33">
         <v>35.5</v>
@@ -6698,7 +6710,7 @@
         <v>85</v>
       </c>
       <c r="S34">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T34">
         <v>100</v>
@@ -6769,7 +6781,7 @@
         <v>100</v>
       </c>
       <c r="T35">
-        <v>95.2</v>
+        <v>96.8</v>
       </c>
       <c r="U35">
         <v>93.5</v>
@@ -6834,10 +6846,10 @@
         <v>80</v>
       </c>
       <c r="S36">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="T36">
-        <v>95.2</v>
+        <v>96.8</v>
       </c>
       <c r="U36">
         <v>90.3</v>
@@ -6905,7 +6917,7 @@
         <v>100</v>
       </c>
       <c r="T37">
-        <v>97.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="U37">
         <v>100</v>
@@ -6970,10 +6982,10 @@
         <v>95</v>
       </c>
       <c r="S38">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T38">
-        <v>95.2</v>
+        <v>96.8</v>
       </c>
       <c r="U38">
         <v>100</v>
@@ -7041,7 +7053,7 @@
         <v>100</v>
       </c>
       <c r="T39">
-        <v>92.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="U39">
         <v>74.2</v>
@@ -7106,7 +7118,7 @@
         <v>97.5</v>
       </c>
       <c r="S40">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T40">
         <v>100</v>
@@ -7174,7 +7186,7 @@
         <v>85</v>
       </c>
       <c r="S41">
-        <v>81.3</v>
+        <v>87.5</v>
       </c>
       <c r="T41">
         <v>95.2</v>
@@ -7390,7 +7402,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>67</v>
@@ -7422,7 +7434,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>68</v>
@@ -7431,19 +7443,19 @@
         <v>40</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E4">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2">
-        <v>60</v>
+        <v>82.5</v>
       </c>
       <c r="G4" s="2">
-        <v>40</v>
+        <v>17.5</v>
       </c>
       <c r="H4">
-        <v>6.3</v>
+        <v>6.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7454,28 +7466,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>69</v>
       </c>
       <c r="C5">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E5">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F5" s="2">
-        <v>64.09999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="G5" s="2">
-        <v>35.9</v>
+        <v>12.5</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7486,28 +7498,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>70</v>
       </c>
       <c r="C6">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E6">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F6" s="2">
-        <v>77.5</v>
+        <v>92.3</v>
       </c>
       <c r="G6" s="2">
-        <v>22.5</v>
+        <v>7.7</v>
       </c>
       <c r="H6">
-        <v>6.8</v>
+        <v>7.3</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7518,7 +7530,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>71</v>
@@ -7527,19 +7539,19 @@
         <v>40</v>
       </c>
       <c r="D7">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E7">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2">
-        <v>82.5</v>
+        <v>97.5</v>
       </c>
       <c r="G7" s="2">
-        <v>17.5</v>
+        <v>2.5</v>
       </c>
       <c r="H7">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7641,7 +7653,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7673,22 +7685,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920092</v>
+        <v>24330051920101</v>
       </c>
       <c r="B2" t="s">
         <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7696,22 +7708,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920092</v>
+        <v>24330051920101</v>
       </c>
       <c r="B3" t="s">
         <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -7719,22 +7731,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920092</v>
+        <v>24330051920101</v>
       </c>
       <c r="B4" t="s">
         <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7742,22 +7754,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920092</v>
+        <v>24330051920101</v>
       </c>
       <c r="B5" t="s">
         <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7765,22 +7777,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920156</v>
+        <v>24330051920104</v>
       </c>
       <c r="B6" t="s">
         <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7788,16 +7800,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920156</v>
+        <v>24330051920104</v>
       </c>
       <c r="B7" t="s">
         <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D7" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
@@ -7811,19 +7823,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920156</v>
+        <v>24330051920104</v>
       </c>
       <c r="B8" t="s">
         <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D8" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
         <v>69</v>
@@ -7834,22 +7846,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920156</v>
+        <v>24330051920104</v>
       </c>
       <c r="B9" t="s">
         <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D9" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -7857,22 +7869,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920410</v>
+        <v>24330051920393</v>
       </c>
       <c r="B10" t="s">
         <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D10" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -7880,22 +7892,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920410</v>
+        <v>24330051920393</v>
       </c>
       <c r="B11" t="s">
         <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -7903,19 +7915,19 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920410</v>
+        <v>24330051920393</v>
       </c>
       <c r="B12" t="s">
         <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
         <v>69</v>
@@ -7926,22 +7938,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>24330051920410</v>
+        <v>24330051920393</v>
       </c>
       <c r="B13" t="s">
         <v>80</v>
       </c>
       <c r="C13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D13" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -7949,22 +7961,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>24330051920143</v>
+        <v>24330051920156</v>
       </c>
       <c r="B14" t="s">
         <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D14" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -7972,16 +7984,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>24330051920143</v>
+        <v>24330051920156</v>
       </c>
       <c r="B15" t="s">
         <v>81</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D15" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E15" t="s">
         <v>7</v>
@@ -7995,19 +8007,19 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>24330051920143</v>
+        <v>24330051920156</v>
       </c>
       <c r="B16" t="s">
         <v>81</v>
       </c>
       <c r="C16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D16" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
         <v>69</v>
@@ -8018,22 +8030,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>24330051920143</v>
+        <v>24330051920092</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C17" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D17" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -8041,22 +8053,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>24330051920127</v>
+        <v>24330051920092</v>
       </c>
       <c r="B18" t="s">
         <v>82</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D18" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F18" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G18">
         <v>5</v>
@@ -8064,22 +8076,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>24330051920127</v>
+        <v>24330051920392</v>
       </c>
       <c r="B19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D19" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E19" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F19" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G19">
         <v>5</v>
@@ -8087,22 +8099,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>24330051920127</v>
+        <v>24330051920392</v>
       </c>
       <c r="B20" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C20" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D20" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E20" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G20">
         <v>5</v>
@@ -8113,13 +8125,13 @@
         <v>24330051920098</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D21" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E21" t="s">
         <v>7</v>
@@ -8136,19 +8148,19 @@
         <v>24330051920098</v>
       </c>
       <c r="B22" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D22" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E22" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G22">
         <v>5</v>
@@ -8156,22 +8168,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>24330051920098</v>
+        <v>24330051920155</v>
       </c>
       <c r="B23" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C23" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D23" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E23" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F23" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="G23">
         <v>5</v>
@@ -8182,19 +8194,19 @@
         <v>24330051920155</v>
       </c>
       <c r="B24" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C24" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D24" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E24" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F24" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G24">
         <v>5</v>
@@ -8202,22 +8214,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>24330051920155</v>
+        <v>24330051920147</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C25" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D25" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E25" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F25" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G25">
         <v>5</v>
@@ -8225,22 +8237,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>24330051920155</v>
+        <v>24330051920147</v>
       </c>
       <c r="B26" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C26" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D26" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E26" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F26" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G26">
         <v>5</v>
@@ -8248,22 +8260,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>24330051920147</v>
+        <v>24330051920107</v>
       </c>
       <c r="B27" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C27" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D27" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="E27" t="s">
         <v>5</v>
       </c>
       <c r="F27" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G27">
         <v>5</v>
@@ -8271,16 +8283,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>24330051920147</v>
+        <v>24330051920107</v>
       </c>
       <c r="B28" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C28" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D28" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="E28" t="s">
         <v>7</v>
@@ -8294,19 +8306,19 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>24330051920147</v>
+        <v>24330051920113</v>
       </c>
       <c r="B29" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C29" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D29" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="E29" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F29" t="s">
         <v>67</v>
@@ -8320,19 +8332,19 @@
         <v>24330051920113</v>
       </c>
       <c r="B30" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C30" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D30" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E30" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F30" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G30">
         <v>5</v>
@@ -8340,22 +8352,22 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>24330051920113</v>
+        <v>24330051920143</v>
       </c>
       <c r="B31" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C31" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D31" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E31" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F31" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G31">
         <v>5</v>
@@ -8363,22 +8375,22 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>24330051920113</v>
+        <v>24330051920143</v>
       </c>
       <c r="B32" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C32" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D32" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F32" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G32">
         <v>5</v>
@@ -8389,19 +8401,19 @@
         <v>24330051920315</v>
       </c>
       <c r="B33" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C33" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D33" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E33" t="s">
         <v>5</v>
       </c>
       <c r="F33" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G33">
         <v>5</v>
@@ -8412,13 +8424,13 @@
         <v>24330051920315</v>
       </c>
       <c r="B34" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C34" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D34" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E34" t="s">
         <v>7</v>
@@ -8432,22 +8444,22 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>24330051920315</v>
+        <v>24330051920093</v>
       </c>
       <c r="B35" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C35" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D35" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="E35" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F35" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G35">
         <v>5</v>
@@ -8455,16 +8467,16 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>24330051920093</v>
+        <v>24330051920127</v>
       </c>
       <c r="B36" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C36" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D36" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="E36" t="s">
         <v>7</v>
@@ -8478,22 +8490,22 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>24330051920093</v>
+        <v>24330051920142</v>
       </c>
       <c r="B37" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C37" t="s">
         <v>110</v>
       </c>
       <c r="D37" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="E37" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F37" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G37">
         <v>5</v>
@@ -8501,22 +8513,22 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>24330051920122</v>
+        <v>24330051920131</v>
       </c>
       <c r="B38" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C38" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D38" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="E38" t="s">
         <v>5</v>
       </c>
       <c r="F38" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G38">
         <v>5</v>
@@ -8524,22 +8536,22 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>24330051920122</v>
+        <v>24330051920403</v>
       </c>
       <c r="B39" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C39" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D39" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E39" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F39" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G39">
         <v>5</v>
@@ -8547,16 +8559,16 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>24330051920142</v>
+        <v>24330051920149</v>
       </c>
       <c r="B40" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C40" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="D40" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="E40" t="s">
         <v>7</v>
@@ -8570,22 +8582,22 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>24330051920131</v>
+        <v>24330051920305</v>
       </c>
       <c r="B41" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C41" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D41" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="E41" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F41" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G41">
         <v>5</v>
@@ -8593,22 +8605,22 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>24330051920152</v>
+        <v>24330051920144</v>
       </c>
       <c r="B42" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="C42" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D42" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="E42" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F42" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G42">
         <v>5</v>
@@ -8616,19 +8628,19 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>24330051920303</v>
+        <v>24330051920410</v>
       </c>
       <c r="B43" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C43" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D43" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="E43" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F43" t="s">
         <v>67</v>
@@ -8639,22 +8651,22 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>24330051920403</v>
+        <v>24330051920122</v>
       </c>
       <c r="B44" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C44" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D44" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E44" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F44" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G44">
         <v>5</v>
@@ -8662,16 +8674,16 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>24330051920149</v>
+        <v>24330051920306</v>
       </c>
       <c r="B45" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C45" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D45" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="E45" t="s">
         <v>7</v>
@@ -8680,98 +8692,6 @@
         <v>66</v>
       </c>
       <c r="G45">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46">
-        <v>24330051920305</v>
-      </c>
-      <c r="B46" t="s">
-        <v>96</v>
-      </c>
-      <c r="C46" t="s">
-        <v>117</v>
-      </c>
-      <c r="D46" t="s">
-        <v>138</v>
-      </c>
-      <c r="E46" t="s">
-        <v>7</v>
-      </c>
-      <c r="F46" t="s">
-        <v>66</v>
-      </c>
-      <c r="G46">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47">
-        <v>24330051920144</v>
-      </c>
-      <c r="B47" t="s">
-        <v>97</v>
-      </c>
-      <c r="C47" t="s">
-        <v>118</v>
-      </c>
-      <c r="D47" t="s">
-        <v>139</v>
-      </c>
-      <c r="E47" t="s">
-        <v>5</v>
-      </c>
-      <c r="F47" t="s">
-        <v>68</v>
-      </c>
-      <c r="G47">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48">
-        <v>24330051920306</v>
-      </c>
-      <c r="B48" t="s">
-        <v>98</v>
-      </c>
-      <c r="C48" t="s">
-        <v>119</v>
-      </c>
-      <c r="D48" t="s">
-        <v>140</v>
-      </c>
-      <c r="E48" t="s">
-        <v>7</v>
-      </c>
-      <c r="F48" t="s">
-        <v>66</v>
-      </c>
-      <c r="G48">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49">
-        <v>23330051920343</v>
-      </c>
-      <c r="B49" t="s">
-        <v>99</v>
-      </c>
-      <c r="C49" t="s">
-        <v>118</v>
-      </c>
-      <c r="D49" t="s">
-        <v>141</v>
-      </c>
-      <c r="E49" t="s">
-        <v>6</v>
-      </c>
-      <c r="F49" t="s">
-        <v>70</v>
-      </c>
-      <c r="G49">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1AV - Estadisticos 20241.xlsx
+++ b/grupos/1AV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="124">
   <si>
     <t>Materia</t>
   </si>
@@ -218,27 +218,27 @@
     <t>Recursos socioemocionales I</t>
   </si>
   <si>
+    <t>Silva Villegas Mario</t>
+  </si>
+  <si>
     <t>Valerio González Valeria</t>
   </si>
   <si>
-    <t>Silva Villegas Mario</t>
-  </si>
-  <si>
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
+    <t>Breniz Camarillo Lysette</t>
+  </si>
+  <si>
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
-    <t>Breniz Camarillo Lysette</t>
-  </si>
-  <si>
     <t>Faltante Faltante Faltante</t>
   </si>
   <si>
@@ -254,9 +254,6 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>DELGADO</t>
-  </si>
-  <si>
     <t>ESTEVEZ</t>
   </si>
   <si>
@@ -266,66 +263,42 @@
     <t>DURAN</t>
   </si>
   <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
     <t>APARICIO</t>
   </si>
   <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
     <t>CERON</t>
   </si>
   <si>
     <t>CHICO</t>
   </si>
   <si>
+    <t>CHONCOA</t>
+  </si>
+  <si>
     <t>DE JESUS</t>
   </si>
   <si>
     <t>MENDEZ</t>
   </si>
   <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>CAMACHO</t>
-  </si>
-  <si>
-    <t>CHONCOA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
     <t>PANZO</t>
   </si>
   <si>
     <t>RIOS</t>
   </si>
   <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
@@ -335,9 +308,21 @@
     <t>RAMON</t>
   </si>
   <si>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
     <t>OFICIAL</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>MEZA</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
@@ -350,30 +335,6 @@
     <t>PAYRO</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>MEZA</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>TLATEMOHUE</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>CUAHUA</t>
-  </si>
-  <si>
     <t>CORONA</t>
   </si>
   <si>
@@ -383,12 +344,6 @@
     <t>ZEPAHUA</t>
   </si>
   <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
     <t>MARIA ESTEFANIA</t>
   </si>
   <si>
@@ -398,54 +353,36 @@
     <t>EDWARD ALEXIS</t>
   </si>
   <si>
+    <t>CARLOS ARGEL</t>
+  </si>
+  <si>
     <t>VICTOR YAEL</t>
   </si>
   <si>
+    <t>MIRANDA ALIZEET</t>
+  </si>
+  <si>
+    <t>DEREK</t>
+  </si>
+  <si>
+    <t>CARLOS ANTONIO</t>
+  </si>
+  <si>
     <t>LEVI SANTIAGO</t>
   </si>
   <si>
     <t>YARETH</t>
   </si>
   <si>
+    <t>EMMANUEL GUADALUPE</t>
+  </si>
+  <si>
     <t>SANTIAGO</t>
   </si>
   <si>
     <t>RAMSES</t>
   </si>
   <si>
-    <t>MIRANDA ALIZEET</t>
-  </si>
-  <si>
-    <t>DEREK</t>
-  </si>
-  <si>
-    <t>CARLOS ANTONIO</t>
-  </si>
-  <si>
-    <t>CARLOS ARGEL</t>
-  </si>
-  <si>
-    <t>URIEL ARTURO</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>ALEXANDRO</t>
-  </si>
-  <si>
-    <t>EMMANUEL GUADALUPE</t>
-  </si>
-  <si>
-    <t>BRYANA</t>
-  </si>
-  <si>
-    <t>BRAYAN</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
     <t>JOSE ABEL</t>
   </si>
   <si>
@@ -453,9 +390,6 @@
   </si>
   <si>
     <t>UZIEL</t>
-  </si>
-  <si>
-    <t>LUIS ROBERTO</t>
   </si>
 </sst>
 </file>
@@ -1009,7 +943,7 @@
         <v>8</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S4">
         <v>9</v>
@@ -1018,10 +952,10 @@
         <v>7</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W4">
         <v>6</v>
@@ -1030,7 +964,7 @@
         <v>6</v>
       </c>
       <c r="Y4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z4">
         <v>8</v>
@@ -1039,7 +973,7 @@
         <v>6</v>
       </c>
       <c r="AB4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC4">
         <v>7</v>
@@ -1098,7 +1032,7 @@
         <v>7</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S5">
         <v>9</v>
@@ -1107,10 +1041,10 @@
         <v>8</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W5">
         <v>8</v>
@@ -1128,7 +1062,7 @@
         <v>7</v>
       </c>
       <c r="AB5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC5">
         <v>6</v>
@@ -1187,7 +1121,7 @@
         <v>6</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S6">
         <v>9</v>
@@ -1196,10 +1130,10 @@
         <v>8</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W6">
         <v>6</v>
@@ -1217,7 +1151,7 @@
         <v>6</v>
       </c>
       <c r="AB6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC6">
         <v>5</v>
@@ -1276,7 +1210,7 @@
         <v>5</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
         <v>8</v>
@@ -1285,10 +1219,10 @@
         <v>7</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W7">
         <v>7</v>
@@ -1297,7 +1231,7 @@
         <v>6</v>
       </c>
       <c r="Y7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z7">
         <v>7</v>
@@ -1306,7 +1240,7 @@
         <v>6</v>
       </c>
       <c r="AB7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC7">
         <v>6</v>
@@ -1365,7 +1299,7 @@
         <v>5</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S8">
         <v>8</v>
@@ -1374,10 +1308,10 @@
         <v>8</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W8">
         <v>7</v>
@@ -1454,7 +1388,7 @@
         <v>8</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S9">
         <v>9</v>
@@ -1463,10 +1397,10 @@
         <v>8</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W9">
         <v>7</v>
@@ -1475,7 +1409,7 @@
         <v>9</v>
       </c>
       <c r="Y9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z9">
         <v>8</v>
@@ -1484,10 +1418,10 @@
         <v>7</v>
       </c>
       <c r="AB9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC9">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1543,7 +1477,7 @@
         <v>7</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S10">
         <v>5</v>
@@ -1552,10 +1486,10 @@
         <v>5</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W10">
         <v>5</v>
@@ -1573,7 +1507,7 @@
         <v>5</v>
       </c>
       <c r="AB10">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AC10">
         <v>5</v>
@@ -1632,7 +1566,7 @@
         <v>7</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
         <v>9</v>
@@ -1641,10 +1575,10 @@
         <v>8</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W11">
         <v>5</v>
@@ -1653,7 +1587,7 @@
         <v>6</v>
       </c>
       <c r="Y11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z11">
         <v>7</v>
@@ -1721,7 +1655,7 @@
         <v>6</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S12">
         <v>9</v>
@@ -1730,10 +1664,10 @@
         <v>6</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W12">
         <v>6</v>
@@ -1742,7 +1676,7 @@
         <v>6</v>
       </c>
       <c r="Y12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z12">
         <v>6</v>
@@ -1810,7 +1744,7 @@
         <v>6</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
         <v>9</v>
@@ -1819,10 +1753,10 @@
         <v>8</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W13">
         <v>5</v>
@@ -1831,7 +1765,7 @@
         <v>6</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z13">
         <v>8</v>
@@ -1840,10 +1774,10 @@
         <v>8</v>
       </c>
       <c r="AB13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC13">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1899,7 +1833,7 @@
         <v>6</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S14">
         <v>10</v>
@@ -1908,10 +1842,10 @@
         <v>5</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W14">
         <v>6</v>
@@ -1988,7 +1922,7 @@
         <v>7</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
         <v>10</v>
@@ -1997,10 +1931,10 @@
         <v>10</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W15">
         <v>9</v>
@@ -2077,7 +2011,7 @@
         <v>8</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
         <v>10</v>
@@ -2086,10 +2020,10 @@
         <v>9</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W16">
         <v>8</v>
@@ -2166,7 +2100,7 @@
         <v>6</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
         <v>9</v>
@@ -2175,10 +2109,10 @@
         <v>6</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W17">
         <v>5</v>
@@ -2187,7 +2121,7 @@
         <v>6</v>
       </c>
       <c r="Y17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z17">
         <v>6</v>
@@ -2196,7 +2130,7 @@
         <v>6</v>
       </c>
       <c r="AB17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC17">
         <v>6</v>
@@ -2255,7 +2189,7 @@
         <v>7</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S18">
         <v>6</v>
@@ -2264,10 +2198,10 @@
         <v>6</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W18">
         <v>5</v>
@@ -2285,7 +2219,7 @@
         <v>6</v>
       </c>
       <c r="AB18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC18">
         <v>5</v>
@@ -2344,7 +2278,7 @@
         <v>6</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S19">
         <v>8</v>
@@ -2353,10 +2287,10 @@
         <v>5</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W19">
         <v>5</v>
@@ -2374,7 +2308,7 @@
         <v>5</v>
       </c>
       <c r="AB19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC19">
         <v>6</v>
@@ -2433,7 +2367,7 @@
         <v>7</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S20">
         <v>10</v>
@@ -2442,10 +2376,10 @@
         <v>9</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W20">
         <v>7</v>
@@ -2466,7 +2400,7 @@
         <v>8</v>
       </c>
       <c r="AC20">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2522,7 +2456,7 @@
         <v>7</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
         <v>9</v>
@@ -2531,10 +2465,10 @@
         <v>9</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W21">
         <v>7</v>
@@ -2543,7 +2477,7 @@
         <v>7</v>
       </c>
       <c r="Y21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z21">
         <v>8</v>
@@ -2555,7 +2489,7 @@
         <v>8</v>
       </c>
       <c r="AC21">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2611,7 +2545,7 @@
         <v>7</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S22">
         <v>8</v>
@@ -2620,10 +2554,10 @@
         <v>5</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W22">
         <v>5</v>
@@ -2641,7 +2575,7 @@
         <v>5</v>
       </c>
       <c r="AB22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC22">
         <v>5</v>
@@ -2700,7 +2634,7 @@
         <v>7</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S23">
         <v>9</v>
@@ -2709,10 +2643,10 @@
         <v>7</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W23">
         <v>8</v>
@@ -2730,10 +2664,10 @@
         <v>7</v>
       </c>
       <c r="AB23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC23">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2789,7 +2723,7 @@
         <v>7</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S24">
         <v>9</v>
@@ -2798,10 +2732,10 @@
         <v>7</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W24">
         <v>7</v>
@@ -2819,7 +2753,7 @@
         <v>6</v>
       </c>
       <c r="AB24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC24">
         <v>8</v>
@@ -2878,7 +2812,7 @@
         <v>6</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S25">
         <v>10</v>
@@ -2887,10 +2821,10 @@
         <v>6</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W25">
         <v>6</v>
@@ -2899,7 +2833,7 @@
         <v>7</v>
       </c>
       <c r="Y25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z25">
         <v>9</v>
@@ -2967,7 +2901,7 @@
         <v>7</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S26">
         <v>10</v>
@@ -2976,10 +2910,10 @@
         <v>8</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W26">
         <v>7</v>
@@ -2997,10 +2931,10 @@
         <v>7</v>
       </c>
       <c r="AB26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC26">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -3056,7 +2990,7 @@
         <v>7</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S27">
         <v>10</v>
@@ -3065,10 +2999,10 @@
         <v>6</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W27">
         <v>8</v>
@@ -3077,7 +3011,7 @@
         <v>7</v>
       </c>
       <c r="Y27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z27">
         <v>9</v>
@@ -3089,7 +3023,7 @@
         <v>6</v>
       </c>
       <c r="AC27">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -3145,7 +3079,7 @@
         <v>5</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S28">
         <v>5</v>
@@ -3154,10 +3088,10 @@
         <v>5</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W28">
         <v>7</v>
@@ -3175,7 +3109,7 @@
         <v>5</v>
       </c>
       <c r="AB28">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AC28">
         <v>5</v>
@@ -3234,7 +3168,7 @@
         <v>9</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S29">
         <v>9</v>
@@ -3243,10 +3177,10 @@
         <v>8</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W29">
         <v>5</v>
@@ -3255,7 +3189,7 @@
         <v>9</v>
       </c>
       <c r="Y29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z29">
         <v>8</v>
@@ -3267,7 +3201,7 @@
         <v>9</v>
       </c>
       <c r="AC29">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3323,7 +3257,7 @@
         <v>7</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S30">
         <v>9</v>
@@ -3332,10 +3266,10 @@
         <v>6</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W30">
         <v>7</v>
@@ -3344,7 +3278,7 @@
         <v>7</v>
       </c>
       <c r="Y30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z30">
         <v>8</v>
@@ -3356,7 +3290,7 @@
         <v>8</v>
       </c>
       <c r="AC30">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3412,7 +3346,7 @@
         <v>8</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S31">
         <v>9</v>
@@ -3421,10 +3355,10 @@
         <v>7</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W31">
         <v>7</v>
@@ -3442,10 +3376,10 @@
         <v>8</v>
       </c>
       <c r="AB31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC31">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -3501,7 +3435,7 @@
         <v>8</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S32">
         <v>8</v>
@@ -3510,10 +3444,10 @@
         <v>6</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W32">
         <v>5</v>
@@ -3522,7 +3456,7 @@
         <v>8</v>
       </c>
       <c r="Y32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z32">
         <v>8</v>
@@ -3531,10 +3465,10 @@
         <v>6</v>
       </c>
       <c r="AB32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC32">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:29">
@@ -3590,7 +3524,7 @@
         <v>6</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S33">
         <v>8</v>
@@ -3599,10 +3533,10 @@
         <v>5</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W33">
         <v>5</v>
@@ -3679,7 +3613,7 @@
         <v>7</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S34">
         <v>8</v>
@@ -3688,10 +3622,10 @@
         <v>9</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W34">
         <v>5</v>
@@ -3709,7 +3643,7 @@
         <v>7</v>
       </c>
       <c r="AB34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC34">
         <v>7</v>
@@ -3768,7 +3702,7 @@
         <v>8</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S35">
         <v>9</v>
@@ -3777,10 +3711,10 @@
         <v>8</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W35">
         <v>5</v>
@@ -3798,7 +3732,7 @@
         <v>6</v>
       </c>
       <c r="AB35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC35">
         <v>6</v>
@@ -3857,7 +3791,7 @@
         <v>6</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S36">
         <v>8</v>
@@ -3866,10 +3800,10 @@
         <v>7</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W36">
         <v>5</v>
@@ -3887,7 +3821,7 @@
         <v>6</v>
       </c>
       <c r="AB36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC36">
         <v>6</v>
@@ -3946,7 +3880,7 @@
         <v>8</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S37">
         <v>8</v>
@@ -3955,10 +3889,10 @@
         <v>7</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W37">
         <v>5</v>
@@ -3979,7 +3913,7 @@
         <v>9</v>
       </c>
       <c r="AC37">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:29">
@@ -4035,7 +3969,7 @@
         <v>6</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S38">
         <v>8</v>
@@ -4044,10 +3978,10 @@
         <v>8</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W38">
         <v>7</v>
@@ -4056,7 +3990,7 @@
         <v>6</v>
       </c>
       <c r="Y38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z38">
         <v>8</v>
@@ -4124,7 +4058,7 @@
         <v>7</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S39">
         <v>8</v>
@@ -4133,10 +4067,10 @@
         <v>7</v>
       </c>
       <c r="U39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W39">
         <v>5</v>
@@ -4154,7 +4088,7 @@
         <v>6</v>
       </c>
       <c r="AB39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC39">
         <v>6</v>
@@ -4213,7 +4147,7 @@
         <v>6</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S40">
         <v>9</v>
@@ -4222,10 +4156,10 @@
         <v>7</v>
       </c>
       <c r="U40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W40">
         <v>7</v>
@@ -4243,10 +4177,10 @@
         <v>7</v>
       </c>
       <c r="AB40">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC40">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:29">
@@ -4302,7 +4236,7 @@
         <v>6</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S41">
         <v>8</v>
@@ -4311,10 +4245,10 @@
         <v>6</v>
       </c>
       <c r="U41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W41">
         <v>5</v>
@@ -4332,10 +4266,10 @@
         <v>6</v>
       </c>
       <c r="AB41">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC41">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:29">
@@ -4379,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="R42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T42">
         <v>8</v>
       </c>
       <c r="V42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W42">
         <v>8</v>
@@ -4394,7 +4328,7 @@
         <v>6</v>
       </c>
       <c r="Y42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA42">
         <v>7</v>
@@ -4456,7 +4390,7 @@
         <v>6</v>
       </c>
       <c r="R43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S43">
         <v>8</v>
@@ -4465,10 +4399,10 @@
         <v>9</v>
       </c>
       <c r="U43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W43">
         <v>8</v>
@@ -4489,7 +4423,7 @@
         <v>9</v>
       </c>
       <c r="AC43">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -4667,7 +4601,7 @@
         <v>100</v>
       </c>
       <c r="R4">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="S4">
         <v>95.8</v>
@@ -4676,7 +4610,7 @@
         <v>96.8</v>
       </c>
       <c r="U4">
-        <v>96.8</v>
+        <v>95.7</v>
       </c>
       <c r="V4">
         <v>100</v>
@@ -4744,7 +4678,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="U5">
-        <v>90.3</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="V5">
         <v>100</v>
@@ -4803,7 +4737,7 @@
         <v>100</v>
       </c>
       <c r="R6">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="S6">
         <v>91.7</v>
@@ -4812,7 +4746,7 @@
         <v>95.2</v>
       </c>
       <c r="U6">
-        <v>83.90000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="V6">
         <v>100</v>
@@ -4871,7 +4805,7 @@
         <v>100</v>
       </c>
       <c r="R7">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="S7">
         <v>91.7</v>
@@ -4880,7 +4814,7 @@
         <v>96.8</v>
       </c>
       <c r="U7">
-        <v>90.3</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="V7">
         <v>100</v>
@@ -4948,7 +4882,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="U8">
-        <v>90.3</v>
+        <v>84.8</v>
       </c>
       <c r="V8">
         <v>100</v>
@@ -5016,7 +4950,7 @@
         <v>100</v>
       </c>
       <c r="U9">
-        <v>90.3</v>
+        <v>91.3</v>
       </c>
       <c r="V9">
         <v>100</v>
@@ -5075,7 +5009,7 @@
         <v>100</v>
       </c>
       <c r="R10">
-        <v>85</v>
+        <v>83.3</v>
       </c>
       <c r="S10">
         <v>83.3</v>
@@ -5084,7 +5018,7 @@
         <v>93.5</v>
       </c>
       <c r="U10">
-        <v>83.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="V10">
         <v>100</v>
@@ -5143,7 +5077,7 @@
         <v>100</v>
       </c>
       <c r="R11">
-        <v>85</v>
+        <v>83.3</v>
       </c>
       <c r="S11">
         <v>100</v>
@@ -5152,7 +5086,7 @@
         <v>96.8</v>
       </c>
       <c r="U11">
-        <v>87.09999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="V11">
         <v>100</v>
@@ -5211,7 +5145,7 @@
         <v>100</v>
       </c>
       <c r="R12">
-        <v>95</v>
+        <v>93.3</v>
       </c>
       <c r="S12">
         <v>87.5</v>
@@ -5220,7 +5154,7 @@
         <v>95.2</v>
       </c>
       <c r="U12">
-        <v>77.40000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="V12">
         <v>100</v>
@@ -5279,7 +5213,7 @@
         <v>100</v>
       </c>
       <c r="R13">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="S13">
         <v>89.59999999999999</v>
@@ -5288,7 +5222,7 @@
         <v>100</v>
       </c>
       <c r="U13">
-        <v>90.3</v>
+        <v>91.3</v>
       </c>
       <c r="V13">
         <v>100</v>
@@ -5356,7 +5290,7 @@
         <v>100</v>
       </c>
       <c r="U14">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="V14">
         <v>100</v>
@@ -5551,7 +5485,7 @@
         <v>100</v>
       </c>
       <c r="R17">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="S17">
         <v>100</v>
@@ -5560,7 +5494,7 @@
         <v>100</v>
       </c>
       <c r="U17">
-        <v>96.8</v>
+        <v>95.7</v>
       </c>
       <c r="V17">
         <v>100</v>
@@ -5619,7 +5553,7 @@
         <v>100</v>
       </c>
       <c r="R18">
-        <v>85</v>
+        <v>83.3</v>
       </c>
       <c r="S18">
         <v>83.3</v>
@@ -5628,7 +5562,7 @@
         <v>96.8</v>
       </c>
       <c r="U18">
-        <v>67.7</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="V18">
         <v>100</v>
@@ -5687,7 +5621,7 @@
         <v>100</v>
       </c>
       <c r="R19">
-        <v>85</v>
+        <v>83.3</v>
       </c>
       <c r="S19">
         <v>100</v>
@@ -5696,7 +5630,7 @@
         <v>91.90000000000001</v>
       </c>
       <c r="U19">
-        <v>80.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="V19">
         <v>100</v>
@@ -5832,7 +5766,7 @@
         <v>100</v>
       </c>
       <c r="U21">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="V21">
         <v>100</v>
@@ -5891,7 +5825,7 @@
         <v>100</v>
       </c>
       <c r="R22">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="S22">
         <v>97.90000000000001</v>
@@ -5900,7 +5834,7 @@
         <v>95.2</v>
       </c>
       <c r="U22">
-        <v>100</v>
+        <v>91.3</v>
       </c>
       <c r="V22">
         <v>100</v>
@@ -5968,7 +5902,7 @@
         <v>100</v>
       </c>
       <c r="U23">
-        <v>96.8</v>
+        <v>97.8</v>
       </c>
       <c r="V23">
         <v>100</v>
@@ -6027,7 +5961,7 @@
         <v>100</v>
       </c>
       <c r="R24">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="S24">
         <v>95.8</v>
@@ -6036,7 +5970,7 @@
         <v>96.8</v>
       </c>
       <c r="U24">
-        <v>90.3</v>
+        <v>93.5</v>
       </c>
       <c r="V24">
         <v>100</v>
@@ -6095,7 +6029,7 @@
         <v>100</v>
       </c>
       <c r="R25">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="S25">
         <v>95.8</v>
@@ -6104,7 +6038,7 @@
         <v>100</v>
       </c>
       <c r="U25">
-        <v>83.90000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="V25">
         <v>100</v>
@@ -6163,7 +6097,7 @@
         <v>100</v>
       </c>
       <c r="R26">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="S26">
         <v>100</v>
@@ -6172,7 +6106,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="U26">
-        <v>90.3</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="V26">
         <v>100</v>
@@ -6231,7 +6165,7 @@
         <v>100</v>
       </c>
       <c r="R27">
-        <v>85</v>
+        <v>86.7</v>
       </c>
       <c r="S27">
         <v>100</v>
@@ -6240,7 +6174,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="U27">
-        <v>93.5</v>
+        <v>95.7</v>
       </c>
       <c r="V27">
         <v>100</v>
@@ -6299,7 +6233,7 @@
         <v>100</v>
       </c>
       <c r="R28">
-        <v>85</v>
+        <v>56.7</v>
       </c>
       <c r="S28">
         <v>75</v>
@@ -6308,10 +6242,10 @@
         <v>62.9</v>
       </c>
       <c r="U28">
-        <v>77.40000000000001</v>
+        <v>54.3</v>
       </c>
       <c r="V28">
-        <v>100</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -6435,7 +6369,7 @@
         <v>100</v>
       </c>
       <c r="R30">
-        <v>92.5</v>
+        <v>88.3</v>
       </c>
       <c r="S30">
         <v>97.90000000000001</v>
@@ -6444,7 +6378,7 @@
         <v>96.8</v>
       </c>
       <c r="U30">
-        <v>90.3</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="V30">
         <v>100</v>
@@ -6512,7 +6446,7 @@
         <v>100</v>
       </c>
       <c r="U31">
-        <v>100</v>
+        <v>95.7</v>
       </c>
       <c r="V31">
         <v>100</v>
@@ -6571,7 +6505,7 @@
         <v>100</v>
       </c>
       <c r="R32">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="S32">
         <v>100</v>
@@ -6580,7 +6514,7 @@
         <v>93.5</v>
       </c>
       <c r="U32">
-        <v>96.8</v>
+        <v>95.7</v>
       </c>
       <c r="V32">
         <v>100</v>
@@ -6627,7 +6561,7 @@
         <v>92.90000000000001</v>
       </c>
       <c r="N33">
-        <v>35.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="O33">
         <v>100</v>
@@ -6639,7 +6573,7 @@
         <v>100</v>
       </c>
       <c r="R33">
-        <v>85</v>
+        <v>56.7</v>
       </c>
       <c r="S33">
         <v>97.90000000000001</v>
@@ -6648,7 +6582,7 @@
         <v>93.5</v>
       </c>
       <c r="U33">
-        <v>35.5</v>
+        <v>87</v>
       </c>
       <c r="V33">
         <v>100</v>
@@ -6707,7 +6641,7 @@
         <v>100</v>
       </c>
       <c r="R34">
-        <v>85</v>
+        <v>88.3</v>
       </c>
       <c r="S34">
         <v>97.90000000000001</v>
@@ -6716,7 +6650,7 @@
         <v>100</v>
       </c>
       <c r="U34">
-        <v>87.09999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="V34">
         <v>100</v>
@@ -6775,7 +6709,7 @@
         <v>100</v>
       </c>
       <c r="R35">
-        <v>85</v>
+        <v>88.3</v>
       </c>
       <c r="S35">
         <v>100</v>
@@ -6784,7 +6718,7 @@
         <v>96.8</v>
       </c>
       <c r="U35">
-        <v>93.5</v>
+        <v>84.8</v>
       </c>
       <c r="V35">
         <v>100</v>
@@ -6852,7 +6786,7 @@
         <v>96.8</v>
       </c>
       <c r="U36">
-        <v>90.3</v>
+        <v>91.3</v>
       </c>
       <c r="V36">
         <v>100</v>
@@ -6911,7 +6845,7 @@
         <v>100</v>
       </c>
       <c r="R37">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="S37">
         <v>100</v>
@@ -6979,7 +6913,7 @@
         <v>100</v>
       </c>
       <c r="R38">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="S38">
         <v>97.90000000000001</v>
@@ -6988,7 +6922,7 @@
         <v>96.8</v>
       </c>
       <c r="U38">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="V38">
         <v>100</v>
@@ -7047,7 +6981,7 @@
         <v>100</v>
       </c>
       <c r="R39">
-        <v>85</v>
+        <v>83.3</v>
       </c>
       <c r="S39">
         <v>100</v>
@@ -7056,7 +6990,7 @@
         <v>95.2</v>
       </c>
       <c r="U39">
-        <v>74.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="V39">
         <v>100</v>
@@ -7115,7 +7049,7 @@
         <v>100</v>
       </c>
       <c r="R40">
-        <v>97.5</v>
+        <v>93.3</v>
       </c>
       <c r="S40">
         <v>97.90000000000001</v>
@@ -7124,7 +7058,7 @@
         <v>100</v>
       </c>
       <c r="U40">
-        <v>100</v>
+        <v>95.7</v>
       </c>
       <c r="V40">
         <v>100</v>
@@ -7183,7 +7117,7 @@
         <v>100</v>
       </c>
       <c r="R41">
-        <v>85</v>
+        <v>83.3</v>
       </c>
       <c r="S41">
         <v>87.5</v>
@@ -7192,7 +7126,7 @@
         <v>95.2</v>
       </c>
       <c r="U41">
-        <v>74.2</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="V41">
         <v>100</v>
@@ -7239,7 +7173,7 @@
         <v>100</v>
       </c>
       <c r="R42">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="T42">
         <v>100</v>
@@ -7301,7 +7235,7 @@
         <v>100</v>
       </c>
       <c r="R43">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="S43">
         <v>100</v>
@@ -7310,7 +7244,7 @@
         <v>100</v>
       </c>
       <c r="U43">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="V43">
         <v>100</v>
@@ -7370,7 +7304,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>66</v>
@@ -7379,19 +7313,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E2">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F2" s="2">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="G2" s="2">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="H2">
-        <v>5.8</v>
+        <v>6.3</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -7402,7 +7336,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>67</v>
@@ -7411,19 +7345,19 @@
         <v>40</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E3">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F3" s="2">
-        <v>60</v>
+        <v>72.5</v>
       </c>
       <c r="G3" s="2">
-        <v>40</v>
+        <v>27.5</v>
       </c>
       <c r="H3">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -7455,7 +7389,7 @@
         <v>17.5</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7498,7 +7432,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>70</v>
@@ -7507,19 +7441,19 @@
         <v>39</v>
       </c>
       <c r="D6">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" s="2">
-        <v>92.3</v>
+        <v>89.7</v>
       </c>
       <c r="G6" s="2">
-        <v>7.7</v>
+        <v>10.3</v>
       </c>
       <c r="H6">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7530,28 +7464,28 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>71</v>
       </c>
       <c r="C7">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D7">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F7" s="2">
-        <v>97.5</v>
+        <v>92.3</v>
       </c>
       <c r="G7" s="2">
-        <v>2.5</v>
+        <v>7.7</v>
       </c>
       <c r="H7">
-        <v>6.8</v>
+        <v>7.3</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7562,28 +7496,28 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
         <v>72</v>
       </c>
       <c r="C8">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D8">
         <v>39</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="G8" s="2">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="H8">
-        <v>7.7</v>
+        <v>6.8</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7653,7 +7587,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7685,22 +7619,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920101</v>
+        <v>24330051920104</v>
       </c>
       <c r="B2" t="s">
         <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7708,22 +7642,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920101</v>
+        <v>24330051920104</v>
       </c>
       <c r="B3" t="s">
         <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="D3" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -7731,22 +7665,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920101</v>
+        <v>24330051920104</v>
       </c>
       <c r="B4" t="s">
         <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7754,16 +7688,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920101</v>
+        <v>24330051920104</v>
       </c>
       <c r="B5" t="s">
         <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
@@ -7777,22 +7711,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920104</v>
+        <v>24330051920393</v>
       </c>
       <c r="B6" t="s">
         <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7800,22 +7734,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920104</v>
+        <v>24330051920393</v>
       </c>
       <c r="B7" t="s">
         <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7823,16 +7757,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920104</v>
+        <v>24330051920393</v>
       </c>
       <c r="B8" t="s">
         <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -7846,16 +7780,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920104</v>
+        <v>24330051920393</v>
       </c>
       <c r="B9" t="s">
         <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
@@ -7869,22 +7803,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920393</v>
+        <v>24330051920156</v>
       </c>
       <c r="B10" t="s">
         <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D10" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -7892,22 +7826,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920393</v>
+        <v>24330051920156</v>
       </c>
       <c r="B11" t="s">
         <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D11" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -7915,16 +7849,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920393</v>
+        <v>24330051920156</v>
       </c>
       <c r="B12" t="s">
         <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D12" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -7938,22 +7872,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>24330051920393</v>
+        <v>24330051920315</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C13" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D13" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="E13" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -7961,19 +7895,19 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>24330051920156</v>
+        <v>24330051920315</v>
       </c>
       <c r="B14" t="s">
         <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="D14" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="E14" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
         <v>67</v>
@@ -7984,22 +7918,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>24330051920156</v>
+        <v>24330051920315</v>
       </c>
       <c r="B15" t="s">
         <v>81</v>
       </c>
       <c r="C15" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="D15" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="E15" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -8007,22 +7941,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>24330051920156</v>
+        <v>24330051920092</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C16" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="D16" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F16" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -8036,16 +7970,16 @@
         <v>82</v>
       </c>
       <c r="C17" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="D17" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E17" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F17" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -8053,22 +7987,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>24330051920092</v>
+        <v>24330051920107</v>
       </c>
       <c r="B18" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C18" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="D18" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="E18" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F18" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G18">
         <v>5</v>
@@ -8076,19 +8010,19 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>24330051920392</v>
+        <v>24330051920107</v>
       </c>
       <c r="B19" t="s">
         <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="D19" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="E19" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F19" t="s">
         <v>67</v>
@@ -8099,19 +8033,19 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>24330051920392</v>
+        <v>24330051920113</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C20" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="D20" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="E20" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F20" t="s">
         <v>66</v>
@@ -8122,22 +8056,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>24330051920098</v>
+        <v>24330051920113</v>
       </c>
       <c r="B21" t="s">
         <v>84</v>
       </c>
       <c r="C21" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="D21" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="E21" t="s">
         <v>7</v>
       </c>
       <c r="F21" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G21">
         <v>5</v>
@@ -8145,22 +8079,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>24330051920098</v>
+        <v>24330051920143</v>
       </c>
       <c r="B22" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C22" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="D22" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="E22" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F22" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G22">
         <v>5</v>
@@ -8168,19 +8102,19 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>24330051920155</v>
+        <v>24330051920143</v>
       </c>
       <c r="B23" t="s">
         <v>85</v>
       </c>
       <c r="C23" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="D23" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="E23" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F23" t="s">
         <v>67</v>
@@ -8191,19 +8125,19 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>24330051920155</v>
+        <v>24330051920392</v>
       </c>
       <c r="B24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C24" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="D24" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="E24" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F24" t="s">
         <v>66</v>
@@ -8214,22 +8148,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>24330051920147</v>
+        <v>24330051920098</v>
       </c>
       <c r="B25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="D25" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="E25" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F25" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G25">
         <v>5</v>
@@ -8237,19 +8171,19 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>24330051920147</v>
+        <v>24330051920131</v>
       </c>
       <c r="B26" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="D26" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="E26" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F26" t="s">
         <v>66</v>
@@ -8260,22 +8194,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>24330051920107</v>
+        <v>24330051920155</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C27" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="D27" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="E27" t="s">
         <v>5</v>
       </c>
       <c r="F27" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G27">
         <v>5</v>
@@ -8283,19 +8217,19 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>24330051920107</v>
+        <v>24330051920147</v>
       </c>
       <c r="B28" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C28" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="D28" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="E28" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F28" t="s">
         <v>66</v>
@@ -8306,22 +8240,22 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>24330051920113</v>
+        <v>24330051920144</v>
       </c>
       <c r="B29" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="C29" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D29" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="E29" t="s">
         <v>5</v>
       </c>
       <c r="F29" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G29">
         <v>5</v>
@@ -8329,19 +8263,19 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>24330051920113</v>
+        <v>24330051920410</v>
       </c>
       <c r="B30" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C30" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D30" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="E30" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F30" t="s">
         <v>66</v>
@@ -8352,346 +8286,24 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>24330051920143</v>
+        <v>24330051920122</v>
       </c>
       <c r="B31" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C31" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D31" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="E31" t="s">
         <v>5</v>
       </c>
       <c r="F31" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G31">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>24330051920143</v>
-      </c>
-      <c r="B32" t="s">
-        <v>89</v>
-      </c>
-      <c r="C32" t="s">
-        <v>112</v>
-      </c>
-      <c r="D32" t="s">
-        <v>133</v>
-      </c>
-      <c r="E32" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" t="s">
-        <v>66</v>
-      </c>
-      <c r="G32">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>24330051920315</v>
-      </c>
-      <c r="B33" t="s">
-        <v>90</v>
-      </c>
-      <c r="C33" t="s">
-        <v>113</v>
-      </c>
-      <c r="D33" t="s">
-        <v>134</v>
-      </c>
-      <c r="E33" t="s">
-        <v>5</v>
-      </c>
-      <c r="F33" t="s">
-        <v>67</v>
-      </c>
-      <c r="G33">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>24330051920315</v>
-      </c>
-      <c r="B34" t="s">
-        <v>90</v>
-      </c>
-      <c r="C34" t="s">
-        <v>113</v>
-      </c>
-      <c r="D34" t="s">
-        <v>134</v>
-      </c>
-      <c r="E34" t="s">
-        <v>7</v>
-      </c>
-      <c r="F34" t="s">
-        <v>66</v>
-      </c>
-      <c r="G34">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>24330051920093</v>
-      </c>
-      <c r="B35" t="s">
-        <v>91</v>
-      </c>
-      <c r="C35" t="s">
-        <v>114</v>
-      </c>
-      <c r="D35" t="s">
-        <v>135</v>
-      </c>
-      <c r="E35" t="s">
-        <v>7</v>
-      </c>
-      <c r="F35" t="s">
-        <v>66</v>
-      </c>
-      <c r="G35">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>24330051920127</v>
-      </c>
-      <c r="B36" t="s">
-        <v>92</v>
-      </c>
-      <c r="C36" t="s">
-        <v>115</v>
-      </c>
-      <c r="D36" t="s">
-        <v>136</v>
-      </c>
-      <c r="E36" t="s">
-        <v>7</v>
-      </c>
-      <c r="F36" t="s">
-        <v>66</v>
-      </c>
-      <c r="G36">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>24330051920142</v>
-      </c>
-      <c r="B37" t="s">
-        <v>93</v>
-      </c>
-      <c r="C37" t="s">
-        <v>110</v>
-      </c>
-      <c r="D37" t="s">
-        <v>137</v>
-      </c>
-      <c r="E37" t="s">
-        <v>7</v>
-      </c>
-      <c r="F37" t="s">
-        <v>66</v>
-      </c>
-      <c r="G37">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>24330051920131</v>
-      </c>
-      <c r="B38" t="s">
-        <v>94</v>
-      </c>
-      <c r="C38" t="s">
-        <v>110</v>
-      </c>
-      <c r="D38" t="s">
-        <v>138</v>
-      </c>
-      <c r="E38" t="s">
-        <v>5</v>
-      </c>
-      <c r="F38" t="s">
-        <v>67</v>
-      </c>
-      <c r="G38">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>24330051920403</v>
-      </c>
-      <c r="B39" t="s">
-        <v>95</v>
-      </c>
-      <c r="C39" t="s">
-        <v>116</v>
-      </c>
-      <c r="D39" t="s">
-        <v>139</v>
-      </c>
-      <c r="E39" t="s">
-        <v>7</v>
-      </c>
-      <c r="F39" t="s">
-        <v>66</v>
-      </c>
-      <c r="G39">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40">
-        <v>24330051920149</v>
-      </c>
-      <c r="B40" t="s">
-        <v>96</v>
-      </c>
-      <c r="C40" t="s">
-        <v>101</v>
-      </c>
-      <c r="D40" t="s">
-        <v>140</v>
-      </c>
-      <c r="E40" t="s">
-        <v>7</v>
-      </c>
-      <c r="F40" t="s">
-        <v>66</v>
-      </c>
-      <c r="G40">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41">
-        <v>24330051920305</v>
-      </c>
-      <c r="B41" t="s">
-        <v>97</v>
-      </c>
-      <c r="C41" t="s">
-        <v>117</v>
-      </c>
-      <c r="D41" t="s">
-        <v>141</v>
-      </c>
-      <c r="E41" t="s">
-        <v>7</v>
-      </c>
-      <c r="F41" t="s">
-        <v>66</v>
-      </c>
-      <c r="G41">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42">
-        <v>24330051920144</v>
-      </c>
-      <c r="B42" t="s">
-        <v>80</v>
-      </c>
-      <c r="C42" t="s">
-        <v>118</v>
-      </c>
-      <c r="D42" t="s">
-        <v>142</v>
-      </c>
-      <c r="E42" t="s">
-        <v>5</v>
-      </c>
-      <c r="F42" t="s">
-        <v>67</v>
-      </c>
-      <c r="G42">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43">
-        <v>24330051920410</v>
-      </c>
-      <c r="B43" t="s">
-        <v>98</v>
-      </c>
-      <c r="C43" t="s">
-        <v>119</v>
-      </c>
-      <c r="D43" t="s">
-        <v>143</v>
-      </c>
-      <c r="E43" t="s">
-        <v>5</v>
-      </c>
-      <c r="F43" t="s">
-        <v>67</v>
-      </c>
-      <c r="G43">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44">
-        <v>24330051920122</v>
-      </c>
-      <c r="B44" t="s">
-        <v>99</v>
-      </c>
-      <c r="C44" t="s">
-        <v>120</v>
-      </c>
-      <c r="D44" t="s">
-        <v>144</v>
-      </c>
-      <c r="E44" t="s">
-        <v>5</v>
-      </c>
-      <c r="F44" t="s">
-        <v>67</v>
-      </c>
-      <c r="G44">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45">
-        <v>24330051920306</v>
-      </c>
-      <c r="B45" t="s">
-        <v>100</v>
-      </c>
-      <c r="C45" t="s">
-        <v>121</v>
-      </c>
-      <c r="D45" t="s">
-        <v>145</v>
-      </c>
-      <c r="E45" t="s">
-        <v>7</v>
-      </c>
-      <c r="F45" t="s">
-        <v>66</v>
-      </c>
-      <c r="G45">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1AV - Estadisticos 20241.xlsx
+++ b/grupos/1AV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="116">
   <si>
     <t>Materia</t>
   </si>
@@ -218,12 +218,12 @@
     <t>Recursos socioemocionales I</t>
   </si>
   <si>
+    <t>Valerio González Valeria</t>
+  </si>
+  <si>
     <t>Silva Villegas Mario</t>
   </si>
   <si>
-    <t>Valerio González Valeria</t>
-  </si>
-  <si>
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
@@ -254,142 +254,118 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>DURAN</t>
+  </si>
+  <si>
     <t>ESTEVEZ</t>
   </si>
   <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>DURAN</t>
-  </si>
-  <si>
     <t>VENTURA</t>
   </si>
   <si>
     <t>APARICIO</t>
   </si>
   <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>CHICO</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
     <t>PELLICO</t>
   </si>
   <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
     <t>ROSAS</t>
   </si>
   <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>CHICO</t>
-  </si>
-  <si>
-    <t>CHONCOA</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>RIOS</t>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>RAMON</t>
   </si>
   <si>
     <t>JIMENEZ</t>
   </si>
   <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>RAMON</t>
-  </si>
-  <si>
     <t>ZEPEDA</t>
   </si>
   <si>
     <t>OFICIAL</t>
   </si>
   <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>BALDERAS</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
     <t>MEZA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>BALDERAS</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>PAYRO</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
+    <t>ERWIN ISRAEL</t>
+  </si>
+  <si>
+    <t>EDWARD ALEXIS</t>
   </si>
   <si>
     <t>MARIA ESTEFANIA</t>
   </si>
   <si>
-    <t>ERWIN ISRAEL</t>
-  </si>
-  <si>
-    <t>EDWARD ALEXIS</t>
-  </si>
-  <si>
     <t>CARLOS ARGEL</t>
   </si>
   <si>
     <t>VICTOR YAEL</t>
   </si>
   <si>
+    <t>DEREK</t>
+  </si>
+  <si>
+    <t>LEVI SANTIAGO</t>
+  </si>
+  <si>
+    <t>YARETH</t>
+  </si>
+  <si>
+    <t>BRYANA</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>JOSE ABEL</t>
+  </si>
+  <si>
     <t>MIRANDA ALIZEET</t>
   </si>
   <si>
-    <t>DEREK</t>
-  </si>
-  <si>
     <t>CARLOS ANTONIO</t>
-  </si>
-  <si>
-    <t>LEVI SANTIAGO</t>
-  </si>
-  <si>
-    <t>YARETH</t>
-  </si>
-  <si>
-    <t>EMMANUEL GUADALUPE</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>RAMSES</t>
-  </si>
-  <si>
-    <t>JOSE ABEL</t>
-  </si>
-  <si>
-    <t>EDILBERTO</t>
-  </si>
-  <si>
-    <t>UZIEL</t>
   </si>
 </sst>
 </file>
@@ -937,7 +913,7 @@
         <v>9</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q4">
         <v>8</v>
@@ -1026,7 +1002,7 @@
         <v>7</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q5">
         <v>7</v>
@@ -1047,7 +1023,7 @@
         <v>6</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X5">
         <v>8</v>
@@ -1115,7 +1091,7 @@
         <v>6</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q6">
         <v>6</v>
@@ -1204,7 +1180,7 @@
         <v>7</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -1225,7 +1201,7 @@
         <v>6</v>
       </c>
       <c r="W7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X7">
         <v>6</v>
@@ -1293,7 +1269,7 @@
         <v>6</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q8">
         <v>5</v>
@@ -1382,7 +1358,7 @@
         <v>6</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q9">
         <v>8</v>
@@ -1471,7 +1447,7 @@
         <v>6</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q10">
         <v>7</v>
@@ -1560,7 +1536,7 @@
         <v>6</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q11">
         <v>7</v>
@@ -1649,7 +1625,7 @@
         <v>6</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q12">
         <v>6</v>
@@ -1738,7 +1714,7 @@
         <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q13">
         <v>6</v>
@@ -1759,7 +1735,7 @@
         <v>10</v>
       </c>
       <c r="W13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X13">
         <v>6</v>
@@ -1827,7 +1803,7 @@
         <v>7</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q14">
         <v>6</v>
@@ -1916,7 +1892,7 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q15">
         <v>7</v>
@@ -2005,7 +1981,7 @@
         <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
         <v>8</v>
@@ -2094,7 +2070,7 @@
         <v>6</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q17">
         <v>6</v>
@@ -2183,7 +2159,7 @@
         <v>5</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q18">
         <v>7</v>
@@ -2272,7 +2248,7 @@
         <v>6</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q19">
         <v>6</v>
@@ -2361,7 +2337,7 @@
         <v>9</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q20">
         <v>7</v>
@@ -2450,7 +2426,7 @@
         <v>6</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q21">
         <v>7</v>
@@ -2539,7 +2515,7 @@
         <v>5</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
         <v>7</v>
@@ -2560,7 +2536,7 @@
         <v>6</v>
       </c>
       <c r="W22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X22">
         <v>6</v>
@@ -2628,7 +2604,7 @@
         <v>10</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
         <v>7</v>
@@ -2717,7 +2693,7 @@
         <v>8</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q24">
         <v>7</v>
@@ -2806,7 +2782,7 @@
         <v>7</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q25">
         <v>6</v>
@@ -2827,7 +2803,7 @@
         <v>6</v>
       </c>
       <c r="W25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X25">
         <v>7</v>
@@ -2895,7 +2871,7 @@
         <v>9</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
         <v>7</v>
@@ -2984,7 +2960,7 @@
         <v>8</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q27">
         <v>7</v>
@@ -3005,7 +2981,7 @@
         <v>5</v>
       </c>
       <c r="W27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X27">
         <v>7</v>
@@ -3073,7 +3049,7 @@
         <v>5</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q28">
         <v>5</v>
@@ -3094,7 +3070,7 @@
         <v>5</v>
       </c>
       <c r="W28">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X28">
         <v>5</v>
@@ -3162,7 +3138,7 @@
         <v>8</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q29">
         <v>9</v>
@@ -3183,7 +3159,7 @@
         <v>5</v>
       </c>
       <c r="W29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X29">
         <v>9</v>
@@ -3251,7 +3227,7 @@
         <v>8</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q30">
         <v>7</v>
@@ -3340,7 +3316,7 @@
         <v>10</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q31">
         <v>8</v>
@@ -3361,7 +3337,7 @@
         <v>6</v>
       </c>
       <c r="W31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X31">
         <v>8</v>
@@ -3429,7 +3405,7 @@
         <v>7</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q32">
         <v>8</v>
@@ -3518,7 +3494,7 @@
         <v>5</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q33">
         <v>6</v>
@@ -3607,7 +3583,7 @@
         <v>7</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q34">
         <v>7</v>
@@ -3628,7 +3604,7 @@
         <v>6</v>
       </c>
       <c r="W34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X34">
         <v>6</v>
@@ -3696,7 +3672,7 @@
         <v>6</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q35">
         <v>8</v>
@@ -3717,7 +3693,7 @@
         <v>6</v>
       </c>
       <c r="W35">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X35">
         <v>6</v>
@@ -3785,7 +3761,7 @@
         <v>6</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q36">
         <v>6</v>
@@ -3874,7 +3850,7 @@
         <v>7</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q37">
         <v>8</v>
@@ -3895,7 +3871,7 @@
         <v>5</v>
       </c>
       <c r="W37">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X37">
         <v>9</v>
@@ -3963,7 +3939,7 @@
         <v>8</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q38">
         <v>6</v>
@@ -3984,7 +3960,7 @@
         <v>7</v>
       </c>
       <c r="W38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X38">
         <v>6</v>
@@ -4052,7 +4028,7 @@
         <v>7</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q39">
         <v>7</v>
@@ -4073,7 +4049,7 @@
         <v>6</v>
       </c>
       <c r="W39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X39">
         <v>7</v>
@@ -4141,7 +4117,7 @@
         <v>9</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q40">
         <v>6</v>
@@ -4162,7 +4138,7 @@
         <v>5</v>
       </c>
       <c r="W40">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X40">
         <v>6</v>
@@ -4230,7 +4206,7 @@
         <v>8</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q41">
         <v>6</v>
@@ -4307,7 +4283,7 @@
         <v>9</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q42">
         <v>8</v>
@@ -4384,7 +4360,7 @@
         <v>9</v>
       </c>
       <c r="P43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q43">
         <v>6</v>
@@ -4405,7 +4381,7 @@
         <v>7</v>
       </c>
       <c r="W43">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X43">
         <v>6</v>
@@ -4595,7 +4571,7 @@
         <v>100</v>
       </c>
       <c r="P4">
-        <v>85</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q4">
         <v>100</v>
@@ -4663,7 +4639,7 @@
         <v>100</v>
       </c>
       <c r="P5">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q5">
         <v>100</v>
@@ -4731,7 +4707,7 @@
         <v>100</v>
       </c>
       <c r="P6">
-        <v>85</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Q6">
         <v>100</v>
@@ -4799,7 +4775,7 @@
         <v>100</v>
       </c>
       <c r="P7">
-        <v>85</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q7">
         <v>100</v>
@@ -4867,7 +4843,7 @@
         <v>100</v>
       </c>
       <c r="P8">
-        <v>75</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -4935,7 +4911,7 @@
         <v>100</v>
       </c>
       <c r="P9">
-        <v>95</v>
+        <v>93.8</v>
       </c>
       <c r="Q9">
         <v>100</v>
@@ -5003,7 +4979,7 @@
         <v>100</v>
       </c>
       <c r="P10">
-        <v>70</v>
+        <v>81.3</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -5071,7 +5047,7 @@
         <v>100</v>
       </c>
       <c r="P11">
-        <v>80</v>
+        <v>81.3</v>
       </c>
       <c r="Q11">
         <v>100</v>
@@ -5139,7 +5115,7 @@
         <v>100</v>
       </c>
       <c r="P12">
-        <v>70</v>
+        <v>81.3</v>
       </c>
       <c r="Q12">
         <v>100</v>
@@ -5207,7 +5183,7 @@
         <v>100</v>
       </c>
       <c r="P13">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="Q13">
         <v>100</v>
@@ -5275,7 +5251,7 @@
         <v>100</v>
       </c>
       <c r="P14">
-        <v>85</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Q14">
         <v>100</v>
@@ -5343,7 +5319,7 @@
         <v>100</v>
       </c>
       <c r="P15">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -5479,7 +5455,7 @@
         <v>100</v>
       </c>
       <c r="P17">
-        <v>95</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q17">
         <v>100</v>
@@ -5547,7 +5523,7 @@
         <v>100</v>
       </c>
       <c r="P18">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="Q18">
         <v>100</v>
@@ -5615,7 +5591,7 @@
         <v>100</v>
       </c>
       <c r="P19">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="Q19">
         <v>100</v>
@@ -5819,7 +5795,7 @@
         <v>100</v>
       </c>
       <c r="P22">
-        <v>85</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q22">
         <v>100</v>
@@ -5887,7 +5863,7 @@
         <v>100</v>
       </c>
       <c r="P23">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="Q23">
         <v>100</v>
@@ -5955,7 +5931,7 @@
         <v>100</v>
       </c>
       <c r="P24">
-        <v>85</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q24">
         <v>100</v>
@@ -6023,7 +5999,7 @@
         <v>100</v>
       </c>
       <c r="P25">
-        <v>65</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="Q25">
         <v>100</v>
@@ -6091,7 +6067,7 @@
         <v>100</v>
       </c>
       <c r="P26">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="Q26">
         <v>100</v>
@@ -6159,7 +6135,7 @@
         <v>100</v>
       </c>
       <c r="P27">
-        <v>90</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q27">
         <v>100</v>
@@ -6227,7 +6203,7 @@
         <v>100</v>
       </c>
       <c r="P28">
-        <v>50</v>
+        <v>31.3</v>
       </c>
       <c r="Q28">
         <v>100</v>
@@ -6499,7 +6475,7 @@
         <v>100</v>
       </c>
       <c r="P32">
-        <v>75</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Q32">
         <v>100</v>
@@ -6567,7 +6543,7 @@
         <v>100</v>
       </c>
       <c r="P33">
-        <v>75</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Q33">
         <v>100</v>
@@ -6635,7 +6611,7 @@
         <v>100</v>
       </c>
       <c r="P34">
-        <v>85</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q34">
         <v>100</v>
@@ -6703,7 +6679,7 @@
         <v>100</v>
       </c>
       <c r="P35">
-        <v>85</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q35">
         <v>100</v>
@@ -6771,7 +6747,7 @@
         <v>100</v>
       </c>
       <c r="P36">
-        <v>90</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q36">
         <v>100</v>
@@ -6839,7 +6815,7 @@
         <v>100</v>
       </c>
       <c r="P37">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q37">
         <v>100</v>
@@ -6907,7 +6883,7 @@
         <v>100</v>
       </c>
       <c r="P38">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="Q38">
         <v>100</v>
@@ -6975,7 +6951,7 @@
         <v>100</v>
       </c>
       <c r="P39">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="Q39">
         <v>100</v>
@@ -7043,7 +7019,7 @@
         <v>100</v>
       </c>
       <c r="P40">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="Q40">
         <v>100</v>
@@ -7111,7 +7087,7 @@
         <v>100</v>
       </c>
       <c r="P41">
-        <v>70</v>
+        <v>81.3</v>
       </c>
       <c r="Q41">
         <v>100</v>
@@ -7229,7 +7205,7 @@
         <v>100</v>
       </c>
       <c r="P43">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="Q43">
         <v>100</v>
@@ -7304,7 +7280,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>66</v>
@@ -7313,19 +7289,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E2">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F2" s="2">
-        <v>60</v>
+        <v>72.5</v>
       </c>
       <c r="G2" s="2">
-        <v>40</v>
+        <v>27.5</v>
       </c>
       <c r="H2">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -7336,7 +7312,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>67</v>
@@ -7357,7 +7333,7 @@
         <v>27.5</v>
       </c>
       <c r="H3">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -7587,7 +7563,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7619,22 +7595,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920104</v>
+        <v>24330051920393</v>
       </c>
       <c r="B2" t="s">
         <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7642,22 +7618,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920104</v>
+        <v>24330051920393</v>
       </c>
       <c r="B3" t="s">
         <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -7665,16 +7641,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920104</v>
+        <v>24330051920393</v>
       </c>
       <c r="B4" t="s">
         <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -7688,16 +7664,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920104</v>
+        <v>24330051920393</v>
       </c>
       <c r="B5" t="s">
         <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
@@ -7711,22 +7687,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920393</v>
+        <v>24330051920156</v>
       </c>
       <c r="B6" t="s">
         <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7734,22 +7710,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920393</v>
+        <v>24330051920156</v>
       </c>
       <c r="B7" t="s">
         <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7757,16 +7733,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920393</v>
+        <v>24330051920156</v>
       </c>
       <c r="B8" t="s">
         <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D8" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -7780,22 +7756,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920393</v>
+        <v>24330051920104</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -7803,22 +7779,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920156</v>
+        <v>24330051920104</v>
       </c>
       <c r="B10" t="s">
         <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D10" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -7826,22 +7802,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920156</v>
+        <v>24330051920104</v>
       </c>
       <c r="B11" t="s">
         <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D11" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -7849,22 +7825,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920156</v>
+        <v>24330051920315</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D12" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -7878,13 +7854,13 @@
         <v>81</v>
       </c>
       <c r="C13" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D13" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
         <v>66</v>
@@ -7901,16 +7877,16 @@
         <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D14" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -7918,22 +7894,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>24330051920315</v>
+        <v>24330051920092</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C15" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D15" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F15" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -7947,16 +7923,16 @@
         <v>82</v>
       </c>
       <c r="C16" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D16" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E16" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -7964,22 +7940,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>24330051920092</v>
+        <v>24330051920113</v>
       </c>
       <c r="B17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D17" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E17" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -7987,19 +7963,19 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>24330051920107</v>
+        <v>24330051920113</v>
       </c>
       <c r="B18" t="s">
         <v>83</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D18" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="E18" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F18" t="s">
         <v>66</v>
@@ -8010,19 +7986,19 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>24330051920107</v>
+        <v>24330051920392</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D19" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E19" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F19" t="s">
         <v>67</v>
@@ -8033,22 +8009,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>24330051920113</v>
+        <v>24330051920098</v>
       </c>
       <c r="B20" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C20" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D20" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E20" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F20" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G20">
         <v>5</v>
@@ -8056,19 +8032,19 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>24330051920113</v>
+        <v>24330051920403</v>
       </c>
       <c r="B21" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C21" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D21" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E21" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F21" t="s">
         <v>67</v>
@@ -8079,22 +8055,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>24330051920143</v>
+        <v>24330051920155</v>
       </c>
       <c r="B22" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C22" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D22" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E22" t="s">
         <v>5</v>
       </c>
       <c r="F22" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G22">
         <v>5</v>
@@ -8102,19 +8078,19 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>24330051920143</v>
+        <v>24330051920144</v>
       </c>
       <c r="B23" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C23" t="s">
         <v>100</v>
       </c>
       <c r="D23" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E23" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F23" t="s">
         <v>67</v>
@@ -8125,19 +8101,19 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>24330051920392</v>
+        <v>24330051920107</v>
       </c>
       <c r="B24" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s">
         <v>101</v>
       </c>
       <c r="D24" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E24" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F24" t="s">
         <v>66</v>
@@ -8148,162 +8124,24 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>24330051920098</v>
+        <v>24330051920143</v>
       </c>
       <c r="B25" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C25" t="s">
         <v>102</v>
       </c>
       <c r="D25" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E25" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F25" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G25">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>24330051920131</v>
-      </c>
-      <c r="B26" t="s">
-        <v>88</v>
-      </c>
-      <c r="C26" t="s">
-        <v>98</v>
-      </c>
-      <c r="D26" t="s">
-        <v>118</v>
-      </c>
-      <c r="E26" t="s">
-        <v>5</v>
-      </c>
-      <c r="F26" t="s">
-        <v>66</v>
-      </c>
-      <c r="G26">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>24330051920155</v>
-      </c>
-      <c r="B27" t="s">
-        <v>89</v>
-      </c>
-      <c r="C27" t="s">
-        <v>103</v>
-      </c>
-      <c r="D27" t="s">
-        <v>119</v>
-      </c>
-      <c r="E27" t="s">
-        <v>5</v>
-      </c>
-      <c r="F27" t="s">
-        <v>66</v>
-      </c>
-      <c r="G27">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>24330051920147</v>
-      </c>
-      <c r="B28" t="s">
-        <v>90</v>
-      </c>
-      <c r="C28" t="s">
-        <v>104</v>
-      </c>
-      <c r="D28" t="s">
-        <v>120</v>
-      </c>
-      <c r="E28" t="s">
-        <v>5</v>
-      </c>
-      <c r="F28" t="s">
-        <v>66</v>
-      </c>
-      <c r="G28">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>24330051920144</v>
-      </c>
-      <c r="B29" t="s">
-        <v>79</v>
-      </c>
-      <c r="C29" t="s">
-        <v>105</v>
-      </c>
-      <c r="D29" t="s">
-        <v>121</v>
-      </c>
-      <c r="E29" t="s">
-        <v>5</v>
-      </c>
-      <c r="F29" t="s">
-        <v>66</v>
-      </c>
-      <c r="G29">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>24330051920410</v>
-      </c>
-      <c r="B30" t="s">
-        <v>91</v>
-      </c>
-      <c r="C30" t="s">
-        <v>106</v>
-      </c>
-      <c r="D30" t="s">
-        <v>122</v>
-      </c>
-      <c r="E30" t="s">
-        <v>5</v>
-      </c>
-      <c r="F30" t="s">
-        <v>66</v>
-      </c>
-      <c r="G30">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>24330051920122</v>
-      </c>
-      <c r="B31" t="s">
-        <v>92</v>
-      </c>
-      <c r="C31" t="s">
-        <v>107</v>
-      </c>
-      <c r="D31" t="s">
-        <v>123</v>
-      </c>
-      <c r="E31" t="s">
-        <v>5</v>
-      </c>
-      <c r="F31" t="s">
-        <v>66</v>
-      </c>
-      <c r="G31">
         <v>5</v>
       </c>
     </row>
